--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3097"/>
+  <dimension ref="A1:C3121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40693,6 +40693,318 @@
         <v>31.2</v>
       </c>
     </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr">
+        <is>
+          <t>2026-09-12 00:00</t>
+        </is>
+      </c>
+      <c r="B3098" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3098" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr">
+        <is>
+          <t>2026-09-12 01:00</t>
+        </is>
+      </c>
+      <c r="B3099" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3099" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr">
+        <is>
+          <t>2026-09-12 02:00</t>
+        </is>
+      </c>
+      <c r="B3100" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3100" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr">
+        <is>
+          <t>2026-09-12 03:00</t>
+        </is>
+      </c>
+      <c r="B3101" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3101" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:00</t>
+        </is>
+      </c>
+      <c r="B3102" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3102" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr">
+        <is>
+          <t>2026-09-12 05:00</t>
+        </is>
+      </c>
+      <c r="B3103" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3103" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr">
+        <is>
+          <t>2026-09-12 06:00</t>
+        </is>
+      </c>
+      <c r="B3104" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3104" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr">
+        <is>
+          <t>2026-09-12 07:00</t>
+        </is>
+      </c>
+      <c r="B3105" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3105" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:00</t>
+        </is>
+      </c>
+      <c r="B3106" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3106" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr">
+        <is>
+          <t>2026-09-12 09:00</t>
+        </is>
+      </c>
+      <c r="B3107" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3107" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:00</t>
+        </is>
+      </c>
+      <c r="B3108" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3108" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:00</t>
+        </is>
+      </c>
+      <c r="B3109" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3109" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:00</t>
+        </is>
+      </c>
+      <c r="B3110" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3110" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:00</t>
+        </is>
+      </c>
+      <c r="B3111" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3111" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr">
+        <is>
+          <t>2026-09-12 14:00</t>
+        </is>
+      </c>
+      <c r="B3112" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3112" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr">
+        <is>
+          <t>2026-09-12 15:00</t>
+        </is>
+      </c>
+      <c r="B3113" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3113" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr">
+        <is>
+          <t>2026-09-12 16:00</t>
+        </is>
+      </c>
+      <c r="B3114" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3114" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr">
+        <is>
+          <t>2026-09-12 17:00</t>
+        </is>
+      </c>
+      <c r="B3115" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3115" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:00</t>
+        </is>
+      </c>
+      <c r="B3116" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3116" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr">
+        <is>
+          <t>2026-09-12 19:00</t>
+        </is>
+      </c>
+      <c r="B3117" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3117" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr">
+        <is>
+          <t>2026-09-12 20:00</t>
+        </is>
+      </c>
+      <c r="B3118" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3118" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr">
+        <is>
+          <t>2026-09-12 21:00</t>
+        </is>
+      </c>
+      <c r="B3119" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3119" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:00</t>
+        </is>
+      </c>
+      <c r="B3120" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3120" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr">
+        <is>
+          <t>2026-09-12 23:00</t>
+        </is>
+      </c>
+      <c r="B3121" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3121" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3121"/>
+  <dimension ref="A1:C3145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41005,6 +41005,318 @@
         <v>40.7</v>
       </c>
     </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr">
+        <is>
+          <t>2026-09-13 00:00</t>
+        </is>
+      </c>
+      <c r="B3122" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3122" t="n">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr">
+        <is>
+          <t>2026-09-13 01:00</t>
+        </is>
+      </c>
+      <c r="B3123" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3123" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr">
+        <is>
+          <t>2026-09-13 02:00</t>
+        </is>
+      </c>
+      <c r="B3124" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3124" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="inlineStr">
+        <is>
+          <t>2026-09-13 03:00</t>
+        </is>
+      </c>
+      <c r="B3125" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3125" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:00</t>
+        </is>
+      </c>
+      <c r="B3126" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3126" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="inlineStr">
+        <is>
+          <t>2026-09-13 05:00</t>
+        </is>
+      </c>
+      <c r="B3127" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3127" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" t="inlineStr">
+        <is>
+          <t>2026-09-13 06:00</t>
+        </is>
+      </c>
+      <c r="B3128" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3128" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="inlineStr">
+        <is>
+          <t>2026-09-13 07:00</t>
+        </is>
+      </c>
+      <c r="B3129" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3129" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="inlineStr">
+        <is>
+          <t>2026-09-13 08:00</t>
+        </is>
+      </c>
+      <c r="B3130" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3130" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:00</t>
+        </is>
+      </c>
+      <c r="B3131" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3131" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="inlineStr">
+        <is>
+          <t>2026-09-13 10:00</t>
+        </is>
+      </c>
+      <c r="B3132" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3132" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:00</t>
+        </is>
+      </c>
+      <c r="B3133" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3133" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:00</t>
+        </is>
+      </c>
+      <c r="B3134" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3134" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:00</t>
+        </is>
+      </c>
+      <c r="B3135" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3135" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" t="inlineStr">
+        <is>
+          <t>2026-09-13 14:00</t>
+        </is>
+      </c>
+      <c r="B3136" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3136" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" t="inlineStr">
+        <is>
+          <t>2026-09-13 15:00</t>
+        </is>
+      </c>
+      <c r="B3137" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3137" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" t="inlineStr">
+        <is>
+          <t>2026-09-13 16:00</t>
+        </is>
+      </c>
+      <c r="B3138" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3138" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" t="inlineStr">
+        <is>
+          <t>2026-09-13 17:00</t>
+        </is>
+      </c>
+      <c r="B3139" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3139" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" t="inlineStr">
+        <is>
+          <t>2026-09-13 18:00</t>
+        </is>
+      </c>
+      <c r="B3140" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3140" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" t="inlineStr">
+        <is>
+          <t>2026-09-13 19:00</t>
+        </is>
+      </c>
+      <c r="B3141" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3141" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" t="inlineStr">
+        <is>
+          <t>2026-09-13 20:00</t>
+        </is>
+      </c>
+      <c r="B3142" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3142" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" t="inlineStr">
+        <is>
+          <t>2026-09-13 21:00</t>
+        </is>
+      </c>
+      <c r="B3143" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3143" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:00</t>
+        </is>
+      </c>
+      <c r="B3144" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3144" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:00</t>
+        </is>
+      </c>
+      <c r="B3145" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3145" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3145"/>
+  <dimension ref="A1:C3169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41317,6 +41317,318 @@
         <v>50.4</v>
       </c>
     </row>
+    <row r="3146">
+      <c r="A3146" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00</t>
+        </is>
+      </c>
+      <c r="B3146" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3146" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" t="inlineStr">
+        <is>
+          <t>2026-09-14 01:00</t>
+        </is>
+      </c>
+      <c r="B3147" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3147" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" t="inlineStr">
+        <is>
+          <t>2026-09-14 02:00</t>
+        </is>
+      </c>
+      <c r="B3148" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3148" t="n">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" t="inlineStr">
+        <is>
+          <t>2026-09-14 03:00</t>
+        </is>
+      </c>
+      <c r="B3149" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3149" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="3150">
+      <c r="A3150" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:00</t>
+        </is>
+      </c>
+      <c r="B3150" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3150" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="3151">
+      <c r="A3151" t="inlineStr">
+        <is>
+          <t>2026-09-14 05:00</t>
+        </is>
+      </c>
+      <c r="B3151" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3151" t="n">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" t="inlineStr">
+        <is>
+          <t>2026-09-14 06:00</t>
+        </is>
+      </c>
+      <c r="B3152" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3152" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:00</t>
+        </is>
+      </c>
+      <c r="B3153" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3153" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:00</t>
+        </is>
+      </c>
+      <c r="B3154" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3154" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="3155">
+      <c r="A3155" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:00</t>
+        </is>
+      </c>
+      <c r="B3155" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3155" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" t="inlineStr">
+        <is>
+          <t>2026-09-14 10:00</t>
+        </is>
+      </c>
+      <c r="B3156" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3156" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:00</t>
+        </is>
+      </c>
+      <c r="B3157" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3157" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="3158">
+      <c r="A3158" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:00</t>
+        </is>
+      </c>
+      <c r="B3158" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3158" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="3159">
+      <c r="A3159" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:00</t>
+        </is>
+      </c>
+      <c r="B3159" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3159" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:00</t>
+        </is>
+      </c>
+      <c r="B3160" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3160" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:00</t>
+        </is>
+      </c>
+      <c r="B3161" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3161" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00</t>
+        </is>
+      </c>
+      <c r="B3162" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3162" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="3163">
+      <c r="A3163" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:00</t>
+        </is>
+      </c>
+      <c r="B3163" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3163" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="3164">
+      <c r="A3164" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:00</t>
+        </is>
+      </c>
+      <c r="B3164" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3164" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="3165">
+      <c r="A3165" t="inlineStr">
+        <is>
+          <t>2026-09-14 19:00</t>
+        </is>
+      </c>
+      <c r="B3165" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3165" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="3166">
+      <c r="A3166" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:00</t>
+        </is>
+      </c>
+      <c r="B3166" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3166" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="3167">
+      <c r="A3167" t="inlineStr">
+        <is>
+          <t>2026-09-14 21:00</t>
+        </is>
+      </c>
+      <c r="B3167" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3167" t="n">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="3168">
+      <c r="A3168" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:00</t>
+        </is>
+      </c>
+      <c r="B3168" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3168" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" t="inlineStr">
+        <is>
+          <t>2026-09-14 23:00</t>
+        </is>
+      </c>
+      <c r="B3169" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3169" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3169"/>
+  <dimension ref="A1:C3193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41629,6 +41629,318 @@
         <v>48.1</v>
       </c>
     </row>
+    <row r="3170">
+      <c r="A3170" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00</t>
+        </is>
+      </c>
+      <c r="B3170" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3170" t="n">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:00</t>
+        </is>
+      </c>
+      <c r="B3171" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3171" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="3172">
+      <c r="A3172" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:00</t>
+        </is>
+      </c>
+      <c r="B3172" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3172" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:00</t>
+        </is>
+      </c>
+      <c r="B3173" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3173" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:00</t>
+        </is>
+      </c>
+      <c r="B3174" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3174" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:00</t>
+        </is>
+      </c>
+      <c r="B3175" t="n">
+        <v>109</v>
+      </c>
+      <c r="C3175" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:00</t>
+        </is>
+      </c>
+      <c r="B3176" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3176" t="n">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:00</t>
+        </is>
+      </c>
+      <c r="B3177" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3177" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:00</t>
+        </is>
+      </c>
+      <c r="B3178" t="n">
+        <v>109</v>
+      </c>
+      <c r="C3178" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="3179">
+      <c r="A3179" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:00</t>
+        </is>
+      </c>
+      <c r="B3179" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3179" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:00</t>
+        </is>
+      </c>
+      <c r="B3180" t="n">
+        <v>111</v>
+      </c>
+      <c r="C3180" t="n">
+        <v>52.6</v>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00</t>
+        </is>
+      </c>
+      <c r="B3181" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3181" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:00</t>
+        </is>
+      </c>
+      <c r="B3182" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3182" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:00</t>
+        </is>
+      </c>
+      <c r="B3183" t="n">
+        <v>118</v>
+      </c>
+      <c r="C3183" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="3184">
+      <c r="A3184" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:00</t>
+        </is>
+      </c>
+      <c r="B3184" t="n">
+        <v>121</v>
+      </c>
+      <c r="C3184" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="3185">
+      <c r="A3185" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:00</t>
+        </is>
+      </c>
+      <c r="B3185" t="n">
+        <v>123</v>
+      </c>
+      <c r="C3185" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:00</t>
+        </is>
+      </c>
+      <c r="B3186" t="n">
+        <v>126</v>
+      </c>
+      <c r="C3186" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="3187">
+      <c r="A3187" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:00</t>
+        </is>
+      </c>
+      <c r="B3187" t="n">
+        <v>136</v>
+      </c>
+      <c r="C3187" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:00</t>
+        </is>
+      </c>
+      <c r="B3188" t="n">
+        <v>152</v>
+      </c>
+      <c r="C3188" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:00</t>
+        </is>
+      </c>
+      <c r="B3189" t="n">
+        <v>151</v>
+      </c>
+      <c r="C3189" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="3190">
+      <c r="A3190" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:00</t>
+        </is>
+      </c>
+      <c r="B3190" t="n">
+        <v>138</v>
+      </c>
+      <c r="C3190" t="n">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:00</t>
+        </is>
+      </c>
+      <c r="B3191" t="n">
+        <v>138</v>
+      </c>
+      <c r="C3191" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00</t>
+        </is>
+      </c>
+      <c r="B3192" t="n">
+        <v>141</v>
+      </c>
+      <c r="C3192" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:00</t>
+        </is>
+      </c>
+      <c r="B3193" t="n">
+        <v>144</v>
+      </c>
+      <c r="C3193" t="n">
+        <v>84.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3193"/>
+  <dimension ref="A1:C3217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41941,6 +41941,318 @@
         <v>84.5</v>
       </c>
     </row>
+    <row r="3194">
+      <c r="A3194" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00</t>
+        </is>
+      </c>
+      <c r="B3194" t="n">
+        <v>148</v>
+      </c>
+      <c r="C3194" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" t="inlineStr">
+        <is>
+          <t>2026-09-16 01:00</t>
+        </is>
+      </c>
+      <c r="B3195" t="n">
+        <v>151</v>
+      </c>
+      <c r="C3195" t="n">
+        <v>86.09999999999999</v>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="inlineStr">
+        <is>
+          <t>2026-09-16 02:00</t>
+        </is>
+      </c>
+      <c r="B3196" t="n">
+        <v>152</v>
+      </c>
+      <c r="C3196" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" t="inlineStr">
+        <is>
+          <t>2026-09-16 03:00</t>
+        </is>
+      </c>
+      <c r="B3197" t="n">
+        <v>154</v>
+      </c>
+      <c r="C3197" t="n">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:00</t>
+        </is>
+      </c>
+      <c r="B3198" t="n">
+        <v>155</v>
+      </c>
+      <c r="C3198" t="n">
+        <v>87.8</v>
+      </c>
+    </row>
+    <row r="3199">
+      <c r="A3199" t="inlineStr">
+        <is>
+          <t>2026-09-16 05:00</t>
+        </is>
+      </c>
+      <c r="B3199" t="n">
+        <v>157</v>
+      </c>
+      <c r="C3199" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="3200">
+      <c r="A3200" t="inlineStr">
+        <is>
+          <t>2026-09-16 06:00</t>
+        </is>
+      </c>
+      <c r="B3200" t="n">
+        <v>158</v>
+      </c>
+      <c r="C3200" t="n">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" t="inlineStr">
+        <is>
+          <t>2026-09-16 07:00</t>
+        </is>
+      </c>
+      <c r="B3201" t="n">
+        <v>160</v>
+      </c>
+      <c r="C3201" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" t="inlineStr">
+        <is>
+          <t>2026-09-16 08:00</t>
+        </is>
+      </c>
+      <c r="B3202" t="n">
+        <v>161</v>
+      </c>
+      <c r="C3202" t="n">
+        <v>78.7</v>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:00</t>
+        </is>
+      </c>
+      <c r="B3203" t="n">
+        <v>161</v>
+      </c>
+      <c r="C3203" t="n">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:00</t>
+        </is>
+      </c>
+      <c r="B3204" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3204" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="3205">
+      <c r="A3205" t="inlineStr">
+        <is>
+          <t>2026-09-16 11:00</t>
+        </is>
+      </c>
+      <c r="B3205" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3205" t="n">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:00</t>
+        </is>
+      </c>
+      <c r="B3206" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3206" t="n">
+        <v>52.7</v>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:00</t>
+        </is>
+      </c>
+      <c r="B3207" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3207" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B3208" t="n">
+        <v>161</v>
+      </c>
+      <c r="C3208" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:00</t>
+        </is>
+      </c>
+      <c r="B3209" t="n">
+        <v>161</v>
+      </c>
+      <c r="C3209" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:00</t>
+        </is>
+      </c>
+      <c r="B3210" t="n">
+        <v>161</v>
+      </c>
+      <c r="C3210" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:00</t>
+        </is>
+      </c>
+      <c r="B3211" t="n">
+        <v>161</v>
+      </c>
+      <c r="C3211" t="n">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="3212">
+      <c r="A3212" t="inlineStr">
+        <is>
+          <t>2026-09-16 18:00</t>
+        </is>
+      </c>
+      <c r="B3212" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3212" t="n">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="3213">
+      <c r="A3213" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:00</t>
+        </is>
+      </c>
+      <c r="B3213" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3213" t="n">
+        <v>89.40000000000001</v>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" t="inlineStr">
+        <is>
+          <t>2026-09-16 20:00</t>
+        </is>
+      </c>
+      <c r="B3214" t="n">
+        <v>163</v>
+      </c>
+      <c r="C3214" t="n">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00</t>
+        </is>
+      </c>
+      <c r="B3215" t="n">
+        <v>163</v>
+      </c>
+      <c r="C3215" t="n">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="3216">
+      <c r="A3216" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:00</t>
+        </is>
+      </c>
+      <c r="B3216" t="n">
+        <v>163</v>
+      </c>
+      <c r="C3216" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="3217">
+      <c r="A3217" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:00</t>
+        </is>
+      </c>
+      <c r="B3217" t="n">
+        <v>163</v>
+      </c>
+      <c r="C3217" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3217"/>
+  <dimension ref="A1:C3241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42253,6 +42253,318 @@
         <v>54.1</v>
       </c>
     </row>
+    <row r="3218">
+      <c r="A3218" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00</t>
+        </is>
+      </c>
+      <c r="B3218" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3218" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3219">
+      <c r="A3219" t="inlineStr">
+        <is>
+          <t>2026-09-17 01:00</t>
+        </is>
+      </c>
+      <c r="B3219" t="n">
+        <v>161</v>
+      </c>
+      <c r="C3219" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="3220">
+      <c r="A3220" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:00</t>
+        </is>
+      </c>
+      <c r="B3220" t="n">
+        <v>160</v>
+      </c>
+      <c r="C3220" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="3221">
+      <c r="A3221" t="inlineStr">
+        <is>
+          <t>2026-09-17 03:00</t>
+        </is>
+      </c>
+      <c r="B3221" t="n">
+        <v>159</v>
+      </c>
+      <c r="C3221" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="3222">
+      <c r="A3222" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:00</t>
+        </is>
+      </c>
+      <c r="B3222" t="n">
+        <v>158</v>
+      </c>
+      <c r="C3222" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="3223">
+      <c r="A3223" t="inlineStr">
+        <is>
+          <t>2026-09-17 05:00</t>
+        </is>
+      </c>
+      <c r="B3223" t="n">
+        <v>157</v>
+      </c>
+      <c r="C3223" t="n">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="3224">
+      <c r="A3224" t="inlineStr">
+        <is>
+          <t>2026-09-17 06:00</t>
+        </is>
+      </c>
+      <c r="B3224" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3224" t="n">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:00</t>
+        </is>
+      </c>
+      <c r="B3225" t="n">
+        <v>155</v>
+      </c>
+      <c r="C3225" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" t="inlineStr">
+        <is>
+          <t>2026-09-17 08:00</t>
+        </is>
+      </c>
+      <c r="B3226" t="n">
+        <v>154</v>
+      </c>
+      <c r="C3226" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:00</t>
+        </is>
+      </c>
+      <c r="B3227" t="n">
+        <v>152</v>
+      </c>
+      <c r="C3227" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:00</t>
+        </is>
+      </c>
+      <c r="B3228" t="n">
+        <v>152</v>
+      </c>
+      <c r="C3228" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" t="inlineStr">
+        <is>
+          <t>2026-09-17 11:00</t>
+        </is>
+      </c>
+      <c r="B3229" t="n">
+        <v>151</v>
+      </c>
+      <c r="C3229" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:00</t>
+        </is>
+      </c>
+      <c r="B3230" t="n">
+        <v>150</v>
+      </c>
+      <c r="C3230" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="3231">
+      <c r="A3231" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00</t>
+        </is>
+      </c>
+      <c r="B3231" t="n">
+        <v>147</v>
+      </c>
+      <c r="C3231" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="3232">
+      <c r="A3232" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:00</t>
+        </is>
+      </c>
+      <c r="B3232" t="n">
+        <v>144</v>
+      </c>
+      <c r="C3232" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="3233">
+      <c r="A3233" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:00</t>
+        </is>
+      </c>
+      <c r="B3233" t="n">
+        <v>141</v>
+      </c>
+      <c r="C3233" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="3234">
+      <c r="A3234" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:00</t>
+        </is>
+      </c>
+      <c r="B3234" t="n">
+        <v>137</v>
+      </c>
+      <c r="C3234" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="3235">
+      <c r="A3235" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:00</t>
+        </is>
+      </c>
+      <c r="B3235" t="n">
+        <v>134</v>
+      </c>
+      <c r="C3235" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3236">
+      <c r="A3236" t="inlineStr">
+        <is>
+          <t>2026-09-17 18:00</t>
+        </is>
+      </c>
+      <c r="B3236" t="n">
+        <v>129</v>
+      </c>
+      <c r="C3236" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3237">
+      <c r="A3237" t="inlineStr">
+        <is>
+          <t>2026-09-17 19:00</t>
+        </is>
+      </c>
+      <c r="B3237" t="n">
+        <v>123</v>
+      </c>
+      <c r="C3237" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="3238">
+      <c r="A3238" t="inlineStr">
+        <is>
+          <t>2026-09-17 20:00</t>
+        </is>
+      </c>
+      <c r="B3238" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3238" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="3239">
+      <c r="A3239" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:00</t>
+        </is>
+      </c>
+      <c r="B3239" t="n">
+        <v>111</v>
+      </c>
+      <c r="C3239" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="3240">
+      <c r="A3240" t="inlineStr">
+        <is>
+          <t>2026-09-17 22:00</t>
+        </is>
+      </c>
+      <c r="B3240" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3240" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="3241">
+      <c r="A3241" t="inlineStr">
+        <is>
+          <t>2026-09-17 23:00</t>
+        </is>
+      </c>
+      <c r="B3241" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3241" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3241"/>
+  <dimension ref="A1:C3265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42565,6 +42565,318 @@
         <v>34.6</v>
       </c>
     </row>
+    <row r="3242">
+      <c r="A3242" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00</t>
+        </is>
+      </c>
+      <c r="B3242" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3242" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" t="inlineStr">
+        <is>
+          <t>2026-09-18 01:00</t>
+        </is>
+      </c>
+      <c r="B3243" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3243" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" t="inlineStr">
+        <is>
+          <t>2026-09-18 02:00</t>
+        </is>
+      </c>
+      <c r="B3244" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3244" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" t="inlineStr">
+        <is>
+          <t>2026-09-18 03:00</t>
+        </is>
+      </c>
+      <c r="B3245" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3245" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="3246">
+      <c r="A3246" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:00</t>
+        </is>
+      </c>
+      <c r="B3246" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3246" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="3247">
+      <c r="A3247" t="inlineStr">
+        <is>
+          <t>2026-09-18 05:00</t>
+        </is>
+      </c>
+      <c r="B3247" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3247" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3248">
+      <c r="A3248" t="inlineStr">
+        <is>
+          <t>2026-09-18 06:00</t>
+        </is>
+      </c>
+      <c r="B3248" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3248" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" t="inlineStr">
+        <is>
+          <t>2026-09-18 07:00</t>
+        </is>
+      </c>
+      <c r="B3249" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3249" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="3250">
+      <c r="A3250" t="inlineStr">
+        <is>
+          <t>2026-09-18 08:00</t>
+        </is>
+      </c>
+      <c r="B3250" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3250" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:00</t>
+        </is>
+      </c>
+      <c r="B3251" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3251" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="3252">
+      <c r="A3252" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:00</t>
+        </is>
+      </c>
+      <c r="B3252" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3252" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:00</t>
+        </is>
+      </c>
+      <c r="B3253" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3253" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:00</t>
+        </is>
+      </c>
+      <c r="B3254" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3254" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:00</t>
+        </is>
+      </c>
+      <c r="B3255" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3255" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" t="inlineStr">
+        <is>
+          <t>2026-09-18 14:00</t>
+        </is>
+      </c>
+      <c r="B3256" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3256" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3257">
+      <c r="A3257" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:00</t>
+        </is>
+      </c>
+      <c r="B3257" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3257" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:00</t>
+        </is>
+      </c>
+      <c r="B3258" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3258" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="3259">
+      <c r="A3259" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:00</t>
+        </is>
+      </c>
+      <c r="B3259" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3259" t="n">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:00</t>
+        </is>
+      </c>
+      <c r="B3260" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3260" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:00</t>
+        </is>
+      </c>
+      <c r="B3261" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3261" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" t="inlineStr">
+        <is>
+          <t>2026-09-18 20:00</t>
+        </is>
+      </c>
+      <c r="B3262" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3262" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="3263">
+      <c r="A3263" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:00</t>
+        </is>
+      </c>
+      <c r="B3263" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3263" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="3264">
+      <c r="A3264" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:00</t>
+        </is>
+      </c>
+      <c r="B3264" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3264" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="3265">
+      <c r="A3265" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:00</t>
+        </is>
+      </c>
+      <c r="B3265" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3265" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3265"/>
+  <dimension ref="A1:C3289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42877,6 +42877,318 @@
         <v>30.7</v>
       </c>
     </row>
+    <row r="3266">
+      <c r="A3266" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00</t>
+        </is>
+      </c>
+      <c r="B3266" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3266" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="3267">
+      <c r="A3267" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:00</t>
+        </is>
+      </c>
+      <c r="B3267" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3267" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="3268">
+      <c r="A3268" t="inlineStr">
+        <is>
+          <t>2026-09-19 02:00</t>
+        </is>
+      </c>
+      <c r="B3268" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3268" t="n">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="3269">
+      <c r="A3269" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:00</t>
+        </is>
+      </c>
+      <c r="B3269" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3269" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="3270">
+      <c r="A3270" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:00</t>
+        </is>
+      </c>
+      <c r="B3270" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3270" t="n">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="3271">
+      <c r="A3271" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:00</t>
+        </is>
+      </c>
+      <c r="B3271" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3271" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3272">
+      <c r="A3272" t="inlineStr">
+        <is>
+          <t>2026-09-19 06:00</t>
+        </is>
+      </c>
+      <c r="B3272" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3272" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="3273">
+      <c r="A3273" t="inlineStr">
+        <is>
+          <t>2026-09-19 07:00</t>
+        </is>
+      </c>
+      <c r="B3273" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3273" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="3274">
+      <c r="A3274" t="inlineStr">
+        <is>
+          <t>2026-09-19 08:00</t>
+        </is>
+      </c>
+      <c r="B3274" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3274" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="3275">
+      <c r="A3275" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:00</t>
+        </is>
+      </c>
+      <c r="B3275" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3275" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="3276">
+      <c r="A3276" t="inlineStr">
+        <is>
+          <t>2026-09-19 10:00</t>
+        </is>
+      </c>
+      <c r="B3276" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3276" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="3277">
+      <c r="A3277" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:00</t>
+        </is>
+      </c>
+      <c r="B3277" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3277" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="3278">
+      <c r="A3278" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:00</t>
+        </is>
+      </c>
+      <c r="B3278" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3278" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="3279">
+      <c r="A3279" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:00</t>
+        </is>
+      </c>
+      <c r="B3279" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3279" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3280">
+      <c r="A3280" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:00</t>
+        </is>
+      </c>
+      <c r="B3280" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3280" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="3281">
+      <c r="A3281" t="inlineStr">
+        <is>
+          <t>2026-09-19 15:00</t>
+        </is>
+      </c>
+      <c r="B3281" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3281" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="3282">
+      <c r="A3282" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:00</t>
+        </is>
+      </c>
+      <c r="B3282" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3282" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="3283">
+      <c r="A3283" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:00</t>
+        </is>
+      </c>
+      <c r="B3283" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3283" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="3284">
+      <c r="A3284" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:00</t>
+        </is>
+      </c>
+      <c r="B3284" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3284" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="3285">
+      <c r="A3285" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:00</t>
+        </is>
+      </c>
+      <c r="B3285" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3285" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="3286">
+      <c r="A3286" t="inlineStr">
+        <is>
+          <t>2026-09-19 20:00</t>
+        </is>
+      </c>
+      <c r="B3286" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3286" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="3287">
+      <c r="A3287" t="inlineStr">
+        <is>
+          <t>2026-09-19 21:00</t>
+        </is>
+      </c>
+      <c r="B3287" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3287" t="n">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="3288">
+      <c r="A3288" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:00</t>
+        </is>
+      </c>
+      <c r="B3288" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3288" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="3289">
+      <c r="A3289" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:00</t>
+        </is>
+      </c>
+      <c r="B3289" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3289" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3289"/>
+  <dimension ref="A1:C3313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43189,6 +43189,318 @@
         <v>58.8</v>
       </c>
     </row>
+    <row r="3290">
+      <c r="A3290" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:00</t>
+        </is>
+      </c>
+      <c r="B3290" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3290" t="n">
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="3291">
+      <c r="A3291" t="inlineStr">
+        <is>
+          <t>2026-09-20 01:00</t>
+        </is>
+      </c>
+      <c r="B3291" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3291" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="3292">
+      <c r="A3292" t="inlineStr">
+        <is>
+          <t>2026-09-20 02:00</t>
+        </is>
+      </c>
+      <c r="B3292" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3292" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="3293">
+      <c r="A3293" t="inlineStr">
+        <is>
+          <t>2026-09-20 03:00</t>
+        </is>
+      </c>
+      <c r="B3293" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3293" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:00</t>
+        </is>
+      </c>
+      <c r="B3294" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3294" t="n">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" t="inlineStr">
+        <is>
+          <t>2026-09-20 05:00</t>
+        </is>
+      </c>
+      <c r="B3295" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3295" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="3296">
+      <c r="A3296" t="inlineStr">
+        <is>
+          <t>2026-09-20 06:00</t>
+        </is>
+      </c>
+      <c r="B3296" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3296" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:00</t>
+        </is>
+      </c>
+      <c r="B3297" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3297" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="3298">
+      <c r="A3298" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:00</t>
+        </is>
+      </c>
+      <c r="B3298" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3298" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:00</t>
+        </is>
+      </c>
+      <c r="B3299" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3299" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:00</t>
+        </is>
+      </c>
+      <c r="B3300" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3300" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:00</t>
+        </is>
+      </c>
+      <c r="B3301" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3301" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="3302">
+      <c r="A3302" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:00</t>
+        </is>
+      </c>
+      <c r="B3302" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3302" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="3303">
+      <c r="A3303" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:00</t>
+        </is>
+      </c>
+      <c r="B3303" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3303" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="3304">
+      <c r="A3304" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:00</t>
+        </is>
+      </c>
+      <c r="B3304" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3304" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="3305">
+      <c r="A3305" t="inlineStr">
+        <is>
+          <t>2026-09-20 15:00</t>
+        </is>
+      </c>
+      <c r="B3305" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3305" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="3306">
+      <c r="A3306" t="inlineStr">
+        <is>
+          <t>2026-09-20 16:00</t>
+        </is>
+      </c>
+      <c r="B3306" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3306" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="3307">
+      <c r="A3307" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:00</t>
+        </is>
+      </c>
+      <c r="B3307" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3307" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="3308">
+      <c r="A3308" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:00</t>
+        </is>
+      </c>
+      <c r="B3308" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3308" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="3309">
+      <c r="A3309" t="inlineStr">
+        <is>
+          <t>2026-09-20 19:00</t>
+        </is>
+      </c>
+      <c r="B3309" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3309" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="3310">
+      <c r="A3310" t="inlineStr">
+        <is>
+          <t>2026-09-20 20:00</t>
+        </is>
+      </c>
+      <c r="B3310" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3310" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="3311">
+      <c r="A3311" t="inlineStr">
+        <is>
+          <t>2026-09-20 21:00</t>
+        </is>
+      </c>
+      <c r="B3311" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3311" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" t="inlineStr">
+        <is>
+          <t>2026-09-20 22:00</t>
+        </is>
+      </c>
+      <c r="B3312" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3312" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" t="inlineStr">
+        <is>
+          <t>2026-09-20 23:00</t>
+        </is>
+      </c>
+      <c r="B3313" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3313" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3313"/>
+  <dimension ref="A1:C3337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43501,6 +43501,318 @@
         <v>28.7</v>
       </c>
     </row>
+    <row r="3314">
+      <c r="A3314" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00</t>
+        </is>
+      </c>
+      <c r="B3314" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3314" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" t="inlineStr">
+        <is>
+          <t>2026-09-21 01:00</t>
+        </is>
+      </c>
+      <c r="B3315" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3315" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3316">
+      <c r="A3316" t="inlineStr">
+        <is>
+          <t>2026-09-21 02:00</t>
+        </is>
+      </c>
+      <c r="B3316" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3316" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" t="inlineStr">
+        <is>
+          <t>2026-09-21 03:00</t>
+        </is>
+      </c>
+      <c r="B3317" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3317" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:00</t>
+        </is>
+      </c>
+      <c r="B3318" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3318" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" t="inlineStr">
+        <is>
+          <t>2026-09-21 05:00</t>
+        </is>
+      </c>
+      <c r="B3319" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3319" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="3320">
+      <c r="A3320" t="inlineStr">
+        <is>
+          <t>2026-09-21 06:00</t>
+        </is>
+      </c>
+      <c r="B3320" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3320" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="3321">
+      <c r="A3321" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:00</t>
+        </is>
+      </c>
+      <c r="B3321" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3321" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:00</t>
+        </is>
+      </c>
+      <c r="B3322" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3322" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:00</t>
+        </is>
+      </c>
+      <c r="B3323" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3323" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" t="inlineStr">
+        <is>
+          <t>2026-09-21 10:00</t>
+        </is>
+      </c>
+      <c r="B3324" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3324" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:00</t>
+        </is>
+      </c>
+      <c r="B3325" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3325" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:00</t>
+        </is>
+      </c>
+      <c r="B3326" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3326" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:00</t>
+        </is>
+      </c>
+      <c r="B3327" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3327" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="3328">
+      <c r="A3328" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:00</t>
+        </is>
+      </c>
+      <c r="B3328" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3328" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="3329">
+      <c r="A3329" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:00</t>
+        </is>
+      </c>
+      <c r="B3329" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3329" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:00</t>
+        </is>
+      </c>
+      <c r="B3330" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3330" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:00</t>
+        </is>
+      </c>
+      <c r="B3331" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3331" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" t="inlineStr">
+        <is>
+          <t>2026-09-21 18:00</t>
+        </is>
+      </c>
+      <c r="B3332" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3332" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:00</t>
+        </is>
+      </c>
+      <c r="B3333" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3333" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" t="inlineStr">
+        <is>
+          <t>2026-09-21 20:00</t>
+        </is>
+      </c>
+      <c r="B3334" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3334" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:00</t>
+        </is>
+      </c>
+      <c r="B3335" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3335" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:00</t>
+        </is>
+      </c>
+      <c r="B3336" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3336" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:00</t>
+        </is>
+      </c>
+      <c r="B3337" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3337" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3337"/>
+  <dimension ref="A1:C3361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43813,6 +43813,318 @@
         <v>33.3</v>
       </c>
     </row>
+    <row r="3338">
+      <c r="A3338" t="inlineStr">
+        <is>
+          <t>2026-09-22 00:00</t>
+        </is>
+      </c>
+      <c r="B3338" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3338" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" t="inlineStr">
+        <is>
+          <t>2026-09-22 01:00</t>
+        </is>
+      </c>
+      <c r="B3339" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3339" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" t="inlineStr">
+        <is>
+          <t>2026-09-22 02:00</t>
+        </is>
+      </c>
+      <c r="B3340" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3340" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" t="inlineStr">
+        <is>
+          <t>2026-09-22 03:00</t>
+        </is>
+      </c>
+      <c r="B3341" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3341" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:00</t>
+        </is>
+      </c>
+      <c r="B3342" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3342" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:00</t>
+        </is>
+      </c>
+      <c r="B3343" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3343" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" t="inlineStr">
+        <is>
+          <t>2026-09-22 06:00</t>
+        </is>
+      </c>
+      <c r="B3344" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3344" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:00</t>
+        </is>
+      </c>
+      <c r="B3345" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3345" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" t="inlineStr">
+        <is>
+          <t>2026-09-22 08:00</t>
+        </is>
+      </c>
+      <c r="B3346" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3346" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:00</t>
+        </is>
+      </c>
+      <c r="B3347" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3347" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:00</t>
+        </is>
+      </c>
+      <c r="B3348" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3348" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:00</t>
+        </is>
+      </c>
+      <c r="B3349" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3349" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:00</t>
+        </is>
+      </c>
+      <c r="B3350" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3350" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="3351">
+      <c r="A3351" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:00</t>
+        </is>
+      </c>
+      <c r="B3351" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3351" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3352">
+      <c r="A3352" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:00</t>
+        </is>
+      </c>
+      <c r="B3352" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3352" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:00</t>
+        </is>
+      </c>
+      <c r="B3353" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3353" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3354">
+      <c r="A3354" t="inlineStr">
+        <is>
+          <t>2026-09-22 16:00</t>
+        </is>
+      </c>
+      <c r="B3354" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3354" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="3355">
+      <c r="A3355" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:00</t>
+        </is>
+      </c>
+      <c r="B3355" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3355" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:00</t>
+        </is>
+      </c>
+      <c r="B3356" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3356" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" t="inlineStr">
+        <is>
+          <t>2026-09-22 19:00</t>
+        </is>
+      </c>
+      <c r="B3357" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3357" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="3358">
+      <c r="A3358" t="inlineStr">
+        <is>
+          <t>2026-09-22 20:00</t>
+        </is>
+      </c>
+      <c r="B3358" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3358" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="3359">
+      <c r="A3359" t="inlineStr">
+        <is>
+          <t>2026-09-22 21:00</t>
+        </is>
+      </c>
+      <c r="B3359" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3359" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" t="inlineStr">
+        <is>
+          <t>2026-09-22 22:00</t>
+        </is>
+      </c>
+      <c r="B3360" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3360" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="3361">
+      <c r="A3361" t="inlineStr">
+        <is>
+          <t>2026-09-22 23:00</t>
+        </is>
+      </c>
+      <c r="B3361" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3361" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3361"/>
+  <dimension ref="A1:C3385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44125,6 +44125,318 @@
         <v>45.8</v>
       </c>
     </row>
+    <row r="3362">
+      <c r="A3362" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00</t>
+        </is>
+      </c>
+      <c r="B3362" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3362" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="3363">
+      <c r="A3363" t="inlineStr">
+        <is>
+          <t>2026-09-23 01:00</t>
+        </is>
+      </c>
+      <c r="B3363" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3363" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="3364">
+      <c r="A3364" t="inlineStr">
+        <is>
+          <t>2026-09-23 02:00</t>
+        </is>
+      </c>
+      <c r="B3364" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3364" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="3365">
+      <c r="A3365" t="inlineStr">
+        <is>
+          <t>2026-09-23 03:00</t>
+        </is>
+      </c>
+      <c r="B3365" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3365" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3366">
+      <c r="A3366" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:00</t>
+        </is>
+      </c>
+      <c r="B3366" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3366" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="3367">
+      <c r="A3367" t="inlineStr">
+        <is>
+          <t>2026-09-23 05:00</t>
+        </is>
+      </c>
+      <c r="B3367" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3367" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:00</t>
+        </is>
+      </c>
+      <c r="B3368" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3368" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:00</t>
+        </is>
+      </c>
+      <c r="B3369" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3369" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3370">
+      <c r="A3370" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:00</t>
+        </is>
+      </c>
+      <c r="B3370" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3370" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="3371">
+      <c r="A3371" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:00</t>
+        </is>
+      </c>
+      <c r="B3371" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3371" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3372">
+      <c r="A3372" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:00</t>
+        </is>
+      </c>
+      <c r="B3372" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3372" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3373">
+      <c r="A3373" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:00</t>
+        </is>
+      </c>
+      <c r="B3373" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3373" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:00</t>
+        </is>
+      </c>
+      <c r="B3374" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3374" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:00</t>
+        </is>
+      </c>
+      <c r="B3375" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3375" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="3376">
+      <c r="A3376" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:00</t>
+        </is>
+      </c>
+      <c r="B3376" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3376" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="3377">
+      <c r="A3377" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:00</t>
+        </is>
+      </c>
+      <c r="B3377" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3377" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="3378">
+      <c r="A3378" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:00</t>
+        </is>
+      </c>
+      <c r="B3378" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3378" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="3379">
+      <c r="A3379" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:00</t>
+        </is>
+      </c>
+      <c r="B3379" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3379" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="3380">
+      <c r="A3380" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:00</t>
+        </is>
+      </c>
+      <c r="B3380" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3380" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="3381">
+      <c r="A3381" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:00</t>
+        </is>
+      </c>
+      <c r="B3381" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3381" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3382">
+      <c r="A3382" t="inlineStr">
+        <is>
+          <t>2026-09-23 20:00</t>
+        </is>
+      </c>
+      <c r="B3382" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3382" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="3383">
+      <c r="A3383" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:00</t>
+        </is>
+      </c>
+      <c r="B3383" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3383" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="3384">
+      <c r="A3384" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00</t>
+        </is>
+      </c>
+      <c r="B3384" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3384" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="3385">
+      <c r="A3385" t="inlineStr">
+        <is>
+          <t>2026-09-23 23:00</t>
+        </is>
+      </c>
+      <c r="B3385" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3385" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3385"/>
+  <dimension ref="A1:C3409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44437,6 +44437,318 @@
         <v>11.8</v>
       </c>
     </row>
+    <row r="3386">
+      <c r="A3386" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:00</t>
+        </is>
+      </c>
+      <c r="B3386" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3386" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="3387">
+      <c r="A3387" t="inlineStr">
+        <is>
+          <t>2026-09-24 01:00</t>
+        </is>
+      </c>
+      <c r="B3387" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3387" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="3388">
+      <c r="A3388" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:00</t>
+        </is>
+      </c>
+      <c r="B3388" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3388" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="3389">
+      <c r="A3389" t="inlineStr">
+        <is>
+          <t>2026-09-24 03:00</t>
+        </is>
+      </c>
+      <c r="B3389" t="n">
+        <v>59</v>
+      </c>
+      <c r="C3389" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="3390">
+      <c r="A3390" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:00</t>
+        </is>
+      </c>
+      <c r="B3390" t="n">
+        <v>58</v>
+      </c>
+      <c r="C3390" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="3391">
+      <c r="A3391" t="inlineStr">
+        <is>
+          <t>2026-09-24 05:00</t>
+        </is>
+      </c>
+      <c r="B3391" t="n">
+        <v>58</v>
+      </c>
+      <c r="C3391" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="3392">
+      <c r="A3392" t="inlineStr">
+        <is>
+          <t>2026-09-24 06:00</t>
+        </is>
+      </c>
+      <c r="B3392" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3392" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="3393">
+      <c r="A3393" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:00</t>
+        </is>
+      </c>
+      <c r="B3393" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3393" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3394">
+      <c r="A3394" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:00</t>
+        </is>
+      </c>
+      <c r="B3394" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3394" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="3395">
+      <c r="A3395" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:00</t>
+        </is>
+      </c>
+      <c r="B3395" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3395" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="3396">
+      <c r="A3396" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="B3396" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3396" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="3397">
+      <c r="A3397" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:00</t>
+        </is>
+      </c>
+      <c r="B3397" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3397" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:00</t>
+        </is>
+      </c>
+      <c r="B3398" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3398" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="3399">
+      <c r="A3399" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:00</t>
+        </is>
+      </c>
+      <c r="B3399" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3399" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:00</t>
+        </is>
+      </c>
+      <c r="B3400" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3400" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="B3401" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3401" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:00</t>
+        </is>
+      </c>
+      <c r="B3402" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3402" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="3403">
+      <c r="A3403" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:00</t>
+        </is>
+      </c>
+      <c r="B3403" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3403" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="3404">
+      <c r="A3404" t="inlineStr">
+        <is>
+          <t>2026-09-24 18:00</t>
+        </is>
+      </c>
+      <c r="B3404" t="n">
+        <v>53</v>
+      </c>
+      <c r="C3404" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="3405">
+      <c r="A3405" t="inlineStr">
+        <is>
+          <t>2026-09-24 19:00</t>
+        </is>
+      </c>
+      <c r="B3405" t="n">
+        <v>53</v>
+      </c>
+      <c r="C3405" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" t="inlineStr">
+        <is>
+          <t>2026-09-24 20:00</t>
+        </is>
+      </c>
+      <c r="B3406" t="n">
+        <v>53</v>
+      </c>
+      <c r="C3406" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:00</t>
+        </is>
+      </c>
+      <c r="B3407" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3407" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:00</t>
+        </is>
+      </c>
+      <c r="B3408" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3408" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:00</t>
+        </is>
+      </c>
+      <c r="B3409" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3409" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3409"/>
+  <dimension ref="A1:C3433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44749,6 +44749,318 @@
         <v>18</v>
       </c>
     </row>
+    <row r="3410">
+      <c r="A3410" t="inlineStr">
+        <is>
+          <t>2026-09-25 00:00</t>
+        </is>
+      </c>
+      <c r="B3410" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3410" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="inlineStr">
+        <is>
+          <t>2026-09-25 01:00</t>
+        </is>
+      </c>
+      <c r="B3411" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3411" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="inlineStr">
+        <is>
+          <t>2026-09-25 02:00</t>
+        </is>
+      </c>
+      <c r="B3412" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3412" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="inlineStr">
+        <is>
+          <t>2026-09-25 03:00</t>
+        </is>
+      </c>
+      <c r="B3413" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3413" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:00</t>
+        </is>
+      </c>
+      <c r="B3414" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3414" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:00</t>
+        </is>
+      </c>
+      <c r="B3415" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3415" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:00</t>
+        </is>
+      </c>
+      <c r="B3416" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3416" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="3417">
+      <c r="A3417" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="B3417" t="n">
+        <v>58</v>
+      </c>
+      <c r="C3417" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" t="inlineStr">
+        <is>
+          <t>2026-09-25 08:00</t>
+        </is>
+      </c>
+      <c r="B3418" t="n">
+        <v>58</v>
+      </c>
+      <c r="C3418" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="3419">
+      <c r="A3419" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:00</t>
+        </is>
+      </c>
+      <c r="B3419" t="n">
+        <v>59</v>
+      </c>
+      <c r="C3419" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3420">
+      <c r="A3420" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:00</t>
+        </is>
+      </c>
+      <c r="B3420" t="n">
+        <v>59</v>
+      </c>
+      <c r="C3420" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:00</t>
+        </is>
+      </c>
+      <c r="B3421" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3421" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3422">
+      <c r="A3422" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:00</t>
+        </is>
+      </c>
+      <c r="B3422" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3422" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="3423">
+      <c r="A3423" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:00</t>
+        </is>
+      </c>
+      <c r="B3423" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3423" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="3424">
+      <c r="A3424" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="B3424" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3424" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="3425">
+      <c r="A3425" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:00</t>
+        </is>
+      </c>
+      <c r="B3425" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3425" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="3426">
+      <c r="A3426" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:00</t>
+        </is>
+      </c>
+      <c r="B3426" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3426" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="3427">
+      <c r="A3427" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:00</t>
+        </is>
+      </c>
+      <c r="B3427" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3427" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="3428">
+      <c r="A3428" t="inlineStr">
+        <is>
+          <t>2026-09-25 18:00</t>
+        </is>
+      </c>
+      <c r="B3428" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3428" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="3429">
+      <c r="A3429" t="inlineStr">
+        <is>
+          <t>2026-09-25 19:00</t>
+        </is>
+      </c>
+      <c r="B3429" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3429" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="3430">
+      <c r="A3430" t="inlineStr">
+        <is>
+          <t>2026-09-25 20:00</t>
+        </is>
+      </c>
+      <c r="B3430" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3430" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="3431">
+      <c r="A3431" t="inlineStr">
+        <is>
+          <t>2026-09-25 21:00</t>
+        </is>
+      </c>
+      <c r="B3431" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3431" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="3432">
+      <c r="A3432" t="inlineStr">
+        <is>
+          <t>2026-09-25 22:00</t>
+        </is>
+      </c>
+      <c r="B3432" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3432" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3433">
+      <c r="A3433" t="inlineStr">
+        <is>
+          <t>2026-09-25 23:00</t>
+        </is>
+      </c>
+      <c r="B3433" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3433" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3433"/>
+  <dimension ref="A1:C3457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45061,6 +45061,318 @@
         <v>21.1</v>
       </c>
     </row>
+    <row r="3434">
+      <c r="A3434" t="inlineStr">
+        <is>
+          <t>2026-09-26 00:00</t>
+        </is>
+      </c>
+      <c r="B3434" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3434" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3435">
+      <c r="A3435" t="inlineStr">
+        <is>
+          <t>2026-09-26 01:00</t>
+        </is>
+      </c>
+      <c r="B3435" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3435" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="3436">
+      <c r="A3436" t="inlineStr">
+        <is>
+          <t>2026-09-26 02:00</t>
+        </is>
+      </c>
+      <c r="B3436" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3436" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="3437">
+      <c r="A3437" t="inlineStr">
+        <is>
+          <t>2026-09-26 03:00</t>
+        </is>
+      </c>
+      <c r="B3437" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3437" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="3438">
+      <c r="A3438" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:00</t>
+        </is>
+      </c>
+      <c r="B3438" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3438" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3439">
+      <c r="A3439" t="inlineStr">
+        <is>
+          <t>2026-09-26 05:00</t>
+        </is>
+      </c>
+      <c r="B3439" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3439" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="3440">
+      <c r="A3440" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:00</t>
+        </is>
+      </c>
+      <c r="B3440" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3440" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="3441">
+      <c r="A3441" t="inlineStr">
+        <is>
+          <t>2026-09-26 07:00</t>
+        </is>
+      </c>
+      <c r="B3441" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3441" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="3442">
+      <c r="A3442" t="inlineStr">
+        <is>
+          <t>2026-09-26 08:00</t>
+        </is>
+      </c>
+      <c r="B3442" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3442" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="3443">
+      <c r="A3443" t="inlineStr">
+        <is>
+          <t>2026-09-26 09:00</t>
+        </is>
+      </c>
+      <c r="B3443" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3443" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3444">
+      <c r="A3444" t="inlineStr">
+        <is>
+          <t>2026-09-26 10:00</t>
+        </is>
+      </c>
+      <c r="B3444" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3444" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3445">
+      <c r="A3445" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:00</t>
+        </is>
+      </c>
+      <c r="B3445" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3445" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="3446">
+      <c r="A3446" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:00</t>
+        </is>
+      </c>
+      <c r="B3446" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3446" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="3447">
+      <c r="A3447" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:00</t>
+        </is>
+      </c>
+      <c r="B3447" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3447" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="3448">
+      <c r="A3448" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:00</t>
+        </is>
+      </c>
+      <c r="B3448" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3448" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="3449">
+      <c r="A3449" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:00</t>
+        </is>
+      </c>
+      <c r="B3449" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3449" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="3450">
+      <c r="A3450" t="inlineStr">
+        <is>
+          <t>2026-09-26 16:00</t>
+        </is>
+      </c>
+      <c r="B3450" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3450" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="3451">
+      <c r="A3451" t="inlineStr">
+        <is>
+          <t>2026-09-26 17:00</t>
+        </is>
+      </c>
+      <c r="B3451" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3451" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:00</t>
+        </is>
+      </c>
+      <c r="B3452" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3452" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="3453">
+      <c r="A3453" t="inlineStr">
+        <is>
+          <t>2026-09-26 19:00</t>
+        </is>
+      </c>
+      <c r="B3453" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3453" t="n">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="3454">
+      <c r="A3454" t="inlineStr">
+        <is>
+          <t>2026-09-26 20:00</t>
+        </is>
+      </c>
+      <c r="B3454" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3454" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="3455">
+      <c r="A3455" t="inlineStr">
+        <is>
+          <t>2026-09-26 21:00</t>
+        </is>
+      </c>
+      <c r="B3455" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3455" t="n">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="3456">
+      <c r="A3456" t="inlineStr">
+        <is>
+          <t>2026-09-26 22:00</t>
+        </is>
+      </c>
+      <c r="B3456" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3456" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="3457">
+      <c r="A3457" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:00</t>
+        </is>
+      </c>
+      <c r="B3457" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3457" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3457"/>
+  <dimension ref="A1:C3481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45373,6 +45373,318 @@
         <v>60.3</v>
       </c>
     </row>
+    <row r="3458">
+      <c r="A3458" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:00</t>
+        </is>
+      </c>
+      <c r="B3458" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3458" t="n">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="3459">
+      <c r="A3459" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:00</t>
+        </is>
+      </c>
+      <c r="B3459" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3459" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="3460">
+      <c r="A3460" t="inlineStr">
+        <is>
+          <t>2026-09-27 02:00</t>
+        </is>
+      </c>
+      <c r="B3460" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3460" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="3461">
+      <c r="A3461" t="inlineStr">
+        <is>
+          <t>2026-09-27 03:00</t>
+        </is>
+      </c>
+      <c r="B3461" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3461" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="3462">
+      <c r="A3462" t="inlineStr">
+        <is>
+          <t>2026-09-27 04:00</t>
+        </is>
+      </c>
+      <c r="B3462" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3462" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="3463">
+      <c r="A3463" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:00</t>
+        </is>
+      </c>
+      <c r="B3463" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3463" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="3464">
+      <c r="A3464" t="inlineStr">
+        <is>
+          <t>2026-09-27 06:00</t>
+        </is>
+      </c>
+      <c r="B3464" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3464" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3465">
+      <c r="A3465" t="inlineStr">
+        <is>
+          <t>2026-09-27 07:00</t>
+        </is>
+      </c>
+      <c r="B3465" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3465" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="3466">
+      <c r="A3466" t="inlineStr">
+        <is>
+          <t>2026-09-27 08:00</t>
+        </is>
+      </c>
+      <c r="B3466" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3466" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="3467">
+      <c r="A3467" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:00</t>
+        </is>
+      </c>
+      <c r="B3467" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3467" t="n">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="3468">
+      <c r="A3468" t="inlineStr">
+        <is>
+          <t>2026-09-27 10:00</t>
+        </is>
+      </c>
+      <c r="B3468" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3468" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="3469">
+      <c r="A3469" t="inlineStr">
+        <is>
+          <t>2026-09-27 11:00</t>
+        </is>
+      </c>
+      <c r="B3469" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3469" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="3470">
+      <c r="A3470" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:00</t>
+        </is>
+      </c>
+      <c r="B3470" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3470" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="3471">
+      <c r="A3471" t="inlineStr">
+        <is>
+          <t>2026-09-27 13:00</t>
+        </is>
+      </c>
+      <c r="B3471" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3471" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="3472">
+      <c r="A3472" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:00</t>
+        </is>
+      </c>
+      <c r="B3472" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3472" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="3473">
+      <c r="A3473" t="inlineStr">
+        <is>
+          <t>2026-09-27 15:00</t>
+        </is>
+      </c>
+      <c r="B3473" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3473" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="3474">
+      <c r="A3474" t="inlineStr">
+        <is>
+          <t>2026-09-27 16:00</t>
+        </is>
+      </c>
+      <c r="B3474" t="n">
+        <v>117</v>
+      </c>
+      <c r="C3474" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="3475">
+      <c r="A3475" t="inlineStr">
+        <is>
+          <t>2026-09-27 17:00</t>
+        </is>
+      </c>
+      <c r="B3475" t="n">
+        <v>117</v>
+      </c>
+      <c r="C3475" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="3476">
+      <c r="A3476" t="inlineStr">
+        <is>
+          <t>2026-09-27 18:00</t>
+        </is>
+      </c>
+      <c r="B3476" t="n">
+        <v>117</v>
+      </c>
+      <c r="C3476" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="3477">
+      <c r="A3477" t="inlineStr">
+        <is>
+          <t>2026-09-27 19:00</t>
+        </is>
+      </c>
+      <c r="B3477" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3477" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" t="inlineStr">
+        <is>
+          <t>2026-09-27 20:00</t>
+        </is>
+      </c>
+      <c r="B3478" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3478" t="n">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="3479">
+      <c r="A3479" t="inlineStr">
+        <is>
+          <t>2026-09-27 21:00</t>
+        </is>
+      </c>
+      <c r="B3479" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3479" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="3480">
+      <c r="A3480" t="inlineStr">
+        <is>
+          <t>2026-09-27 22:00</t>
+        </is>
+      </c>
+      <c r="B3480" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3480" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="3481">
+      <c r="A3481" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:00</t>
+        </is>
+      </c>
+      <c r="B3481" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3481" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3481"/>
+  <dimension ref="A1:C3505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45685,6 +45685,318 @@
         <v>52.4</v>
       </c>
     </row>
+    <row r="3482">
+      <c r="A3482" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:00</t>
+        </is>
+      </c>
+      <c r="B3482" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3482" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="3483">
+      <c r="A3483" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:00</t>
+        </is>
+      </c>
+      <c r="B3483" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3483" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="3484">
+      <c r="A3484" t="inlineStr">
+        <is>
+          <t>2026-09-28 02:00</t>
+        </is>
+      </c>
+      <c r="B3484" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3484" t="n">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="3485">
+      <c r="A3485" t="inlineStr">
+        <is>
+          <t>2026-09-28 03:00</t>
+        </is>
+      </c>
+      <c r="B3485" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3485" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3486">
+      <c r="A3486" t="inlineStr">
+        <is>
+          <t>2026-09-28 04:00</t>
+        </is>
+      </c>
+      <c r="B3486" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3486" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="3487">
+      <c r="A3487" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:00</t>
+        </is>
+      </c>
+      <c r="B3487" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3487" t="n">
+        <v>40.3</v>
+      </c>
+    </row>
+    <row r="3488">
+      <c r="A3488" t="inlineStr">
+        <is>
+          <t>2026-09-28 06:00</t>
+        </is>
+      </c>
+      <c r="B3488" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3488" t="n">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="3489">
+      <c r="A3489" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:00</t>
+        </is>
+      </c>
+      <c r="B3489" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3489" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="3490">
+      <c r="A3490" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:00</t>
+        </is>
+      </c>
+      <c r="B3490" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3490" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="3491">
+      <c r="A3491" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:00</t>
+        </is>
+      </c>
+      <c r="B3491" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3491" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="3492">
+      <c r="A3492" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:00</t>
+        </is>
+      </c>
+      <c r="B3492" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3492" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="3493">
+      <c r="A3493" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:00</t>
+        </is>
+      </c>
+      <c r="B3493" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3493" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="3494">
+      <c r="A3494" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:00</t>
+        </is>
+      </c>
+      <c r="B3494" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3494" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="3495">
+      <c r="A3495" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:00</t>
+        </is>
+      </c>
+      <c r="B3495" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3495" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="3496">
+      <c r="A3496" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:00</t>
+        </is>
+      </c>
+      <c r="B3496" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3496" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="3497">
+      <c r="A3497" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:00</t>
+        </is>
+      </c>
+      <c r="B3497" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3497" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="3498">
+      <c r="A3498" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:00</t>
+        </is>
+      </c>
+      <c r="B3498" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3498" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="3499">
+      <c r="A3499" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:00</t>
+        </is>
+      </c>
+      <c r="B3499" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3499" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="3500">
+      <c r="A3500" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:00</t>
+        </is>
+      </c>
+      <c r="B3500" t="n">
+        <v>118</v>
+      </c>
+      <c r="C3500" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="3501">
+      <c r="A3501" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:00</t>
+        </is>
+      </c>
+      <c r="B3501" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3501" t="n">
+        <v>37.7</v>
+      </c>
+    </row>
+    <row r="3502">
+      <c r="A3502" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:00</t>
+        </is>
+      </c>
+      <c r="B3502" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3502" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="3503">
+      <c r="A3503" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:00</t>
+        </is>
+      </c>
+      <c r="B3503" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3503" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3504">
+      <c r="A3504" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:00</t>
+        </is>
+      </c>
+      <c r="B3504" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3504" t="n">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="3505">
+      <c r="A3505" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:00</t>
+        </is>
+      </c>
+      <c r="B3505" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3505" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3505"/>
+  <dimension ref="A1:C3529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45997,6 +45997,318 @@
         <v>41.8</v>
       </c>
     </row>
+    <row r="3506">
+      <c r="A3506" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:00</t>
+        </is>
+      </c>
+      <c r="B3506" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3506" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="3507">
+      <c r="A3507" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:00</t>
+        </is>
+      </c>
+      <c r="B3507" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3507" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="3508">
+      <c r="A3508" t="inlineStr">
+        <is>
+          <t>2026-09-29 02:00</t>
+        </is>
+      </c>
+      <c r="B3508" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3508" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="3509">
+      <c r="A3509" t="inlineStr">
+        <is>
+          <t>2026-09-29 03:00</t>
+        </is>
+      </c>
+      <c r="B3509" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3509" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="3510">
+      <c r="A3510" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:00</t>
+        </is>
+      </c>
+      <c r="B3510" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3510" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="3511">
+      <c r="A3511" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:00</t>
+        </is>
+      </c>
+      <c r="B3511" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3511" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="3512">
+      <c r="A3512" t="inlineStr">
+        <is>
+          <t>2026-09-29 06:00</t>
+        </is>
+      </c>
+      <c r="B3512" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3512" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="3513">
+      <c r="A3513" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="B3513" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3513" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="3514">
+      <c r="A3514" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:00</t>
+        </is>
+      </c>
+      <c r="B3514" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3514" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="3515">
+      <c r="A3515" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:00</t>
+        </is>
+      </c>
+      <c r="B3515" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3515" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="3516">
+      <c r="A3516" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:00</t>
+        </is>
+      </c>
+      <c r="B3516" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3516" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3517">
+      <c r="A3517" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="B3517" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3517" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="3518">
+      <c r="A3518" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:00</t>
+        </is>
+      </c>
+      <c r="B3518" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3518" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="3519">
+      <c r="A3519" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:00</t>
+        </is>
+      </c>
+      <c r="B3519" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3519" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="3520">
+      <c r="A3520" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="B3520" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3520" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="3521">
+      <c r="A3521" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="B3521" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3521" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3522">
+      <c r="A3522" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:00</t>
+        </is>
+      </c>
+      <c r="B3522" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3522" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="3523">
+      <c r="A3523" t="inlineStr">
+        <is>
+          <t>2026-09-29 17:00</t>
+        </is>
+      </c>
+      <c r="B3523" t="n">
+        <v>125</v>
+      </c>
+      <c r="C3523" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="3524">
+      <c r="A3524" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:00</t>
+        </is>
+      </c>
+      <c r="B3524" t="n">
+        <v>137</v>
+      </c>
+      <c r="C3524" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="3525">
+      <c r="A3525" t="inlineStr">
+        <is>
+          <t>2026-09-29 19:00</t>
+        </is>
+      </c>
+      <c r="B3525" t="n">
+        <v>136</v>
+      </c>
+      <c r="C3525" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="3526">
+      <c r="A3526" t="inlineStr">
+        <is>
+          <t>2026-09-29 20:00</t>
+        </is>
+      </c>
+      <c r="B3526" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3526" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="3527">
+      <c r="A3527" t="inlineStr">
+        <is>
+          <t>2026-09-29 21:00</t>
+        </is>
+      </c>
+      <c r="B3527" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3527" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="3528">
+      <c r="A3528" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:00</t>
+        </is>
+      </c>
+      <c r="B3528" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3528" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="3529">
+      <c r="A3529" t="inlineStr">
+        <is>
+          <t>2026-09-29 23:00</t>
+        </is>
+      </c>
+      <c r="B3529" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3529" t="n">
+        <v>49.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3529"/>
+  <dimension ref="A1:C3553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46309,6 +46309,318 @@
         <v>49.8</v>
       </c>
     </row>
+    <row r="3530">
+      <c r="A3530" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:00</t>
+        </is>
+      </c>
+      <c r="B3530" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3530" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="3531">
+      <c r="A3531" t="inlineStr">
+        <is>
+          <t>2026-09-30 01:00</t>
+        </is>
+      </c>
+      <c r="B3531" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3531" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="3532">
+      <c r="A3532" t="inlineStr">
+        <is>
+          <t>2026-09-30 02:00</t>
+        </is>
+      </c>
+      <c r="B3532" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3532" t="n">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="3533">
+      <c r="A3533" t="inlineStr">
+        <is>
+          <t>2026-09-30 03:00</t>
+        </is>
+      </c>
+      <c r="B3533" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3533" t="n">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="3534">
+      <c r="A3534" t="inlineStr">
+        <is>
+          <t>2026-09-30 04:00</t>
+        </is>
+      </c>
+      <c r="B3534" t="n">
+        <v>107</v>
+      </c>
+      <c r="C3534" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="3535">
+      <c r="A3535" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:00</t>
+        </is>
+      </c>
+      <c r="B3535" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3535" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="3536">
+      <c r="A3536" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:00</t>
+        </is>
+      </c>
+      <c r="B3536" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3536" t="n">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="3537">
+      <c r="A3537" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:00</t>
+        </is>
+      </c>
+      <c r="B3537" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3537" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3538">
+      <c r="A3538" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:00</t>
+        </is>
+      </c>
+      <c r="B3538" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3538" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3539">
+      <c r="A3539" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:00</t>
+        </is>
+      </c>
+      <c r="B3539" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3539" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="3540">
+      <c r="A3540" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:00</t>
+        </is>
+      </c>
+      <c r="B3540" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3540" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="3541">
+      <c r="A3541" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:00</t>
+        </is>
+      </c>
+      <c r="B3541" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3541" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="3542">
+      <c r="A3542" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:00</t>
+        </is>
+      </c>
+      <c r="B3542" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3542" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3543">
+      <c r="A3543" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:00</t>
+        </is>
+      </c>
+      <c r="B3543" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3543" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3544">
+      <c r="A3544" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:00</t>
+        </is>
+      </c>
+      <c r="B3544" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3544" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="3545">
+      <c r="A3545" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:00</t>
+        </is>
+      </c>
+      <c r="B3545" t="n">
+        <v>111</v>
+      </c>
+      <c r="C3545" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="3546">
+      <c r="A3546" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:00</t>
+        </is>
+      </c>
+      <c r="B3546" t="n">
+        <v>122</v>
+      </c>
+      <c r="C3546" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="3547">
+      <c r="A3547" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00</t>
+        </is>
+      </c>
+      <c r="B3547" t="n">
+        <v>146</v>
+      </c>
+      <c r="C3547" t="n">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="3548">
+      <c r="A3548" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:00</t>
+        </is>
+      </c>
+      <c r="B3548" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3548" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="3549">
+      <c r="A3549" t="inlineStr">
+        <is>
+          <t>2026-09-30 19:00</t>
+        </is>
+      </c>
+      <c r="B3549" t="n">
+        <v>157</v>
+      </c>
+      <c r="C3549" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="3550">
+      <c r="A3550" t="inlineStr">
+        <is>
+          <t>2026-09-30 20:00</t>
+        </is>
+      </c>
+      <c r="B3550" t="n">
+        <v>143</v>
+      </c>
+      <c r="C3550" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="3551">
+      <c r="A3551" t="inlineStr">
+        <is>
+          <t>2026-09-30 21:00</t>
+        </is>
+      </c>
+      <c r="B3551" t="n">
+        <v>118</v>
+      </c>
+      <c r="C3551" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="3552">
+      <c r="A3552" t="inlineStr">
+        <is>
+          <t>2026-09-30 22:00</t>
+        </is>
+      </c>
+      <c r="B3552" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3552" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="3553">
+      <c r="A3553" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:00</t>
+        </is>
+      </c>
+      <c r="B3553" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3553" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3553"/>
+  <dimension ref="A1:C3577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46621,6 +46621,318 @@
         <v>32.2</v>
       </c>
     </row>
+    <row r="3554">
+      <c r="A3554" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:00</t>
+        </is>
+      </c>
+      <c r="B3554" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3554" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="3555">
+      <c r="A3555" t="inlineStr">
+        <is>
+          <t>2026-10-01 01:00</t>
+        </is>
+      </c>
+      <c r="B3555" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3555" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="3556">
+      <c r="A3556" t="inlineStr">
+        <is>
+          <t>2026-10-01 02:00</t>
+        </is>
+      </c>
+      <c r="B3556" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3556" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="3557">
+      <c r="A3557" t="inlineStr">
+        <is>
+          <t>2026-10-01 03:00</t>
+        </is>
+      </c>
+      <c r="B3557" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3557" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="3558">
+      <c r="A3558" t="inlineStr">
+        <is>
+          <t>2026-10-01 04:00</t>
+        </is>
+      </c>
+      <c r="B3558" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3558" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="3559">
+      <c r="A3559" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:00</t>
+        </is>
+      </c>
+      <c r="B3559" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3559" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="3560">
+      <c r="A3560" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="B3560" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3560" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="3561">
+      <c r="A3561" t="inlineStr">
+        <is>
+          <t>2026-10-01 07:00</t>
+        </is>
+      </c>
+      <c r="B3561" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3561" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="3562">
+      <c r="A3562" t="inlineStr">
+        <is>
+          <t>2026-10-01 08:00</t>
+        </is>
+      </c>
+      <c r="B3562" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3562" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3563">
+      <c r="A3563" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:00</t>
+        </is>
+      </c>
+      <c r="B3563" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3563" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="3564">
+      <c r="A3564" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:00</t>
+        </is>
+      </c>
+      <c r="B3564" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3564" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="3565">
+      <c r="A3565" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00</t>
+        </is>
+      </c>
+      <c r="B3565" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3565" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="3566">
+      <c r="A3566" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:00</t>
+        </is>
+      </c>
+      <c r="B3566" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3566" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3567">
+      <c r="A3567" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:00</t>
+        </is>
+      </c>
+      <c r="B3567" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3567" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="3568">
+      <c r="A3568" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00</t>
+        </is>
+      </c>
+      <c r="B3568" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3568" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="3569">
+      <c r="A3569" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:00</t>
+        </is>
+      </c>
+      <c r="B3569" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3569" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="3570">
+      <c r="A3570" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:00</t>
+        </is>
+      </c>
+      <c r="B3570" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3570" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="3571">
+      <c r="A3571" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:00</t>
+        </is>
+      </c>
+      <c r="B3571" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3571" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="3572">
+      <c r="A3572" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:00</t>
+        </is>
+      </c>
+      <c r="B3572" t="n">
+        <v>124</v>
+      </c>
+      <c r="C3572" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="3573">
+      <c r="A3573" t="inlineStr">
+        <is>
+          <t>2026-10-01 19:00</t>
+        </is>
+      </c>
+      <c r="B3573" t="n">
+        <v>117</v>
+      </c>
+      <c r="C3573" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="3574">
+      <c r="A3574" t="inlineStr">
+        <is>
+          <t>2026-10-01 20:00</t>
+        </is>
+      </c>
+      <c r="B3574" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3574" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="3575">
+      <c r="A3575" t="inlineStr">
+        <is>
+          <t>2026-10-01 21:00</t>
+        </is>
+      </c>
+      <c r="B3575" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3575" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="3576">
+      <c r="A3576" t="inlineStr">
+        <is>
+          <t>2026-10-01 22:00</t>
+        </is>
+      </c>
+      <c r="B3576" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3576" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="3577">
+      <c r="A3577" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:00</t>
+        </is>
+      </c>
+      <c r="B3577" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3577" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3577"/>
+  <dimension ref="A1:C3601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46933,6 +46933,318 @@
         <v>22.4</v>
       </c>
     </row>
+    <row r="3578">
+      <c r="A3578" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00</t>
+        </is>
+      </c>
+      <c r="B3578" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3578" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="3579">
+      <c r="A3579" t="inlineStr">
+        <is>
+          <t>2026-10-02 01:00</t>
+        </is>
+      </c>
+      <c r="B3579" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3579" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="3580">
+      <c r="A3580" t="inlineStr">
+        <is>
+          <t>2026-10-02 02:00</t>
+        </is>
+      </c>
+      <c r="B3580" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3580" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="3581">
+      <c r="A3581" t="inlineStr">
+        <is>
+          <t>2026-10-02 03:00</t>
+        </is>
+      </c>
+      <c r="B3581" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3581" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="3582">
+      <c r="A3582" t="inlineStr">
+        <is>
+          <t>2026-10-02 04:00</t>
+        </is>
+      </c>
+      <c r="B3582" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3582" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="3583">
+      <c r="A3583" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:00</t>
+        </is>
+      </c>
+      <c r="B3583" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3583" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="3584">
+      <c r="A3584" t="inlineStr">
+        <is>
+          <t>2026-10-02 06:00</t>
+        </is>
+      </c>
+      <c r="B3584" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3584" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="3585">
+      <c r="A3585" t="inlineStr">
+        <is>
+          <t>2026-10-02 07:00</t>
+        </is>
+      </c>
+      <c r="B3585" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3585" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="3586">
+      <c r="A3586" t="inlineStr">
+        <is>
+          <t>2026-10-02 08:00</t>
+        </is>
+      </c>
+      <c r="B3586" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3586" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="3587">
+      <c r="A3587" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:00</t>
+        </is>
+      </c>
+      <c r="B3587" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3587" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3588">
+      <c r="A3588" t="inlineStr">
+        <is>
+          <t>2026-10-02 10:00</t>
+        </is>
+      </c>
+      <c r="B3588" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3588" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="3589">
+      <c r="A3589" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:00</t>
+        </is>
+      </c>
+      <c r="B3589" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3589" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="3590">
+      <c r="A3590" t="inlineStr">
+        <is>
+          <t>2026-10-02 12:00</t>
+        </is>
+      </c>
+      <c r="B3590" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3590" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3591">
+      <c r="A3591" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:00</t>
+        </is>
+      </c>
+      <c r="B3591" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3591" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="3592">
+      <c r="A3592" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:00</t>
+        </is>
+      </c>
+      <c r="B3592" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3592" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="3593">
+      <c r="A3593" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:00</t>
+        </is>
+      </c>
+      <c r="B3593" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3593" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="3594">
+      <c r="A3594" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:00</t>
+        </is>
+      </c>
+      <c r="B3594" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3594" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="3595">
+      <c r="A3595" t="inlineStr">
+        <is>
+          <t>2026-10-02 17:00</t>
+        </is>
+      </c>
+      <c r="B3595" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3595" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="3596">
+      <c r="A3596" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:00</t>
+        </is>
+      </c>
+      <c r="B3596" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3596" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="3597">
+      <c r="A3597" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:00</t>
+        </is>
+      </c>
+      <c r="B3597" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3597" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="3598">
+      <c r="A3598" t="inlineStr">
+        <is>
+          <t>2026-10-02 20:00</t>
+        </is>
+      </c>
+      <c r="B3598" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3598" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="3599">
+      <c r="A3599" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00</t>
+        </is>
+      </c>
+      <c r="B3599" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3599" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="3600">
+      <c r="A3600" t="inlineStr">
+        <is>
+          <t>2026-10-02 22:00</t>
+        </is>
+      </c>
+      <c r="B3600" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3600" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="3601">
+      <c r="A3601" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:00</t>
+        </is>
+      </c>
+      <c r="B3601" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3601" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3601"/>
+  <dimension ref="A1:C3625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47245,6 +47245,318 @@
         <v>22</v>
       </c>
     </row>
+    <row r="3602">
+      <c r="A3602" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:00</t>
+        </is>
+      </c>
+      <c r="B3602" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3602" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3603">
+      <c r="A3603" t="inlineStr">
+        <is>
+          <t>2026-10-03 01:00</t>
+        </is>
+      </c>
+      <c r="B3603" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3603" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3604">
+      <c r="A3604" t="inlineStr">
+        <is>
+          <t>2026-10-03 02:00</t>
+        </is>
+      </c>
+      <c r="B3604" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3604" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="3605">
+      <c r="A3605" t="inlineStr">
+        <is>
+          <t>2026-10-03 03:00</t>
+        </is>
+      </c>
+      <c r="B3605" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3605" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3606">
+      <c r="A3606" t="inlineStr">
+        <is>
+          <t>2026-10-03 04:00</t>
+        </is>
+      </c>
+      <c r="B3606" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3606" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="3607">
+      <c r="A3607" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:00</t>
+        </is>
+      </c>
+      <c r="B3607" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3607" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="3608">
+      <c r="A3608" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:00</t>
+        </is>
+      </c>
+      <c r="B3608" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3608" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3609">
+      <c r="A3609" t="inlineStr">
+        <is>
+          <t>2026-10-03 07:00</t>
+        </is>
+      </c>
+      <c r="B3609" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3609" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3610">
+      <c r="A3610" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:00</t>
+        </is>
+      </c>
+      <c r="B3610" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3610" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="3611">
+      <c r="A3611" t="inlineStr">
+        <is>
+          <t>2026-10-03 09:00</t>
+        </is>
+      </c>
+      <c r="B3611" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3611" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3612">
+      <c r="A3612" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:00</t>
+        </is>
+      </c>
+      <c r="B3612" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3612" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="3613">
+      <c r="A3613" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:00</t>
+        </is>
+      </c>
+      <c r="B3613" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3613" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="3614">
+      <c r="A3614" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00</t>
+        </is>
+      </c>
+      <c r="B3614" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3614" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3615">
+      <c r="A3615" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:00</t>
+        </is>
+      </c>
+      <c r="B3615" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3615" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3616">
+      <c r="A3616" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:00</t>
+        </is>
+      </c>
+      <c r="B3616" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3616" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="3617">
+      <c r="A3617" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:00</t>
+        </is>
+      </c>
+      <c r="B3617" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3617" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="3618">
+      <c r="A3618" t="inlineStr">
+        <is>
+          <t>2026-10-03 16:00</t>
+        </is>
+      </c>
+      <c r="B3618" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3618" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="3619">
+      <c r="A3619" t="inlineStr">
+        <is>
+          <t>2026-10-03 17:00</t>
+        </is>
+      </c>
+      <c r="B3619" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3619" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="3620">
+      <c r="A3620" t="inlineStr">
+        <is>
+          <t>2026-10-03 18:00</t>
+        </is>
+      </c>
+      <c r="B3620" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3620" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3621">
+      <c r="A3621" t="inlineStr">
+        <is>
+          <t>2026-10-03 19:00</t>
+        </is>
+      </c>
+      <c r="B3621" t="n">
+        <v>107</v>
+      </c>
+      <c r="C3621" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3622">
+      <c r="A3622" t="inlineStr">
+        <is>
+          <t>2026-10-03 20:00</t>
+        </is>
+      </c>
+      <c r="B3622" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3622" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="3623">
+      <c r="A3623" t="inlineStr">
+        <is>
+          <t>2026-10-03 21:00</t>
+        </is>
+      </c>
+      <c r="B3623" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3623" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="3624">
+      <c r="A3624" t="inlineStr">
+        <is>
+          <t>2026-10-03 22:00</t>
+        </is>
+      </c>
+      <c r="B3624" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3624" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="3625">
+      <c r="A3625" t="inlineStr">
+        <is>
+          <t>2026-10-03 23:00</t>
+        </is>
+      </c>
+      <c r="B3625" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3625" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3625"/>
+  <dimension ref="A1:C3649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47557,6 +47557,318 @@
         <v>38.8</v>
       </c>
     </row>
+    <row r="3626">
+      <c r="A3626" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:00</t>
+        </is>
+      </c>
+      <c r="B3626" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3626" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="3627">
+      <c r="A3627" t="inlineStr">
+        <is>
+          <t>2026-10-04 01:00</t>
+        </is>
+      </c>
+      <c r="B3627" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3627" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="3628">
+      <c r="A3628" t="inlineStr">
+        <is>
+          <t>2026-10-04 02:00</t>
+        </is>
+      </c>
+      <c r="B3628" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3628" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="3629">
+      <c r="A3629" t="inlineStr">
+        <is>
+          <t>2026-10-04 03:00</t>
+        </is>
+      </c>
+      <c r="B3629" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3629" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="3630">
+      <c r="A3630" t="inlineStr">
+        <is>
+          <t>2026-10-04 04:00</t>
+        </is>
+      </c>
+      <c r="B3630" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3630" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="3631">
+      <c r="A3631" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:00</t>
+        </is>
+      </c>
+      <c r="B3631" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3631" t="n">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="3632">
+      <c r="A3632" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:00</t>
+        </is>
+      </c>
+      <c r="B3632" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3632" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="3633">
+      <c r="A3633" t="inlineStr">
+        <is>
+          <t>2026-10-04 07:00</t>
+        </is>
+      </c>
+      <c r="B3633" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3633" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3634">
+      <c r="A3634" t="inlineStr">
+        <is>
+          <t>2026-10-04 08:00</t>
+        </is>
+      </c>
+      <c r="B3634" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3634" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="3635">
+      <c r="A3635" t="inlineStr">
+        <is>
+          <t>2026-10-04 09:00</t>
+        </is>
+      </c>
+      <c r="B3635" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3635" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="3636">
+      <c r="A3636" t="inlineStr">
+        <is>
+          <t>2026-10-04 10:00</t>
+        </is>
+      </c>
+      <c r="B3636" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3636" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="3637">
+      <c r="A3637" t="inlineStr">
+        <is>
+          <t>2026-10-04 11:00</t>
+        </is>
+      </c>
+      <c r="B3637" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3637" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="3638">
+      <c r="A3638" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:00</t>
+        </is>
+      </c>
+      <c r="B3638" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3638" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="3639">
+      <c r="A3639" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:00</t>
+        </is>
+      </c>
+      <c r="B3639" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3639" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="3640">
+      <c r="A3640" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:00</t>
+        </is>
+      </c>
+      <c r="B3640" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3640" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3641">
+      <c r="A3641" t="inlineStr">
+        <is>
+          <t>2026-10-04 15:00</t>
+        </is>
+      </c>
+      <c r="B3641" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3641" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="3642">
+      <c r="A3642" t="inlineStr">
+        <is>
+          <t>2026-10-04 16:00</t>
+        </is>
+      </c>
+      <c r="B3642" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3642" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="3643">
+      <c r="A3643" t="inlineStr">
+        <is>
+          <t>2026-10-04 17:00</t>
+        </is>
+      </c>
+      <c r="B3643" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3643" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="3644">
+      <c r="A3644" t="inlineStr">
+        <is>
+          <t>2026-10-04 18:00</t>
+        </is>
+      </c>
+      <c r="B3644" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3644" t="n">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="3645">
+      <c r="A3645" t="inlineStr">
+        <is>
+          <t>2026-10-04 19:00</t>
+        </is>
+      </c>
+      <c r="B3645" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3645" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="3646">
+      <c r="A3646" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:00</t>
+        </is>
+      </c>
+      <c r="B3646" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3646" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3647">
+      <c r="A3647" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:00</t>
+        </is>
+      </c>
+      <c r="B3647" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3647" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="3648">
+      <c r="A3648" t="inlineStr">
+        <is>
+          <t>2026-10-04 22:00</t>
+        </is>
+      </c>
+      <c r="B3648" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3648" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="3649">
+      <c r="A3649" t="inlineStr">
+        <is>
+          <t>2026-10-04 23:00</t>
+        </is>
+      </c>
+      <c r="B3649" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3649" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3649"/>
+  <dimension ref="A1:C3673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47869,6 +47869,318 @@
         <v>39.6</v>
       </c>
     </row>
+    <row r="3650">
+      <c r="A3650" t="inlineStr">
+        <is>
+          <t>2026-10-05 00:00</t>
+        </is>
+      </c>
+      <c r="B3650" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3650" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="3651">
+      <c r="A3651" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="B3651" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3651" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="3652">
+      <c r="A3652" t="inlineStr">
+        <is>
+          <t>2026-10-05 02:00</t>
+        </is>
+      </c>
+      <c r="B3652" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3652" t="n">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="3653">
+      <c r="A3653" t="inlineStr">
+        <is>
+          <t>2026-10-05 03:00</t>
+        </is>
+      </c>
+      <c r="B3653" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3653" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="3654">
+      <c r="A3654" t="inlineStr">
+        <is>
+          <t>2026-10-05 04:00</t>
+        </is>
+      </c>
+      <c r="B3654" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3654" t="n">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="3655">
+      <c r="A3655" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:00</t>
+        </is>
+      </c>
+      <c r="B3655" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3655" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="3656">
+      <c r="A3656" t="inlineStr">
+        <is>
+          <t>2026-10-05 06:00</t>
+        </is>
+      </c>
+      <c r="B3656" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3656" t="n">
+        <v>37.7</v>
+      </c>
+    </row>
+    <row r="3657">
+      <c r="A3657" t="inlineStr">
+        <is>
+          <t>2026-10-05 07:00</t>
+        </is>
+      </c>
+      <c r="B3657" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3657" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3658">
+      <c r="A3658" t="inlineStr">
+        <is>
+          <t>2026-10-05 08:00</t>
+        </is>
+      </c>
+      <c r="B3658" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3658" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="3659">
+      <c r="A3659" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:00</t>
+        </is>
+      </c>
+      <c r="B3659" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3659" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3660">
+      <c r="A3660" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:00</t>
+        </is>
+      </c>
+      <c r="B3660" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3660" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="3661">
+      <c r="A3661" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:00</t>
+        </is>
+      </c>
+      <c r="B3661" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3661" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="3662">
+      <c r="A3662" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:00</t>
+        </is>
+      </c>
+      <c r="B3662" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3662" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="3663">
+      <c r="A3663" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:00</t>
+        </is>
+      </c>
+      <c r="B3663" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3663" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="3664">
+      <c r="A3664" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:00</t>
+        </is>
+      </c>
+      <c r="B3664" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3664" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3665">
+      <c r="A3665" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:00</t>
+        </is>
+      </c>
+      <c r="B3665" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3665" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="3666">
+      <c r="A3666" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:00</t>
+        </is>
+      </c>
+      <c r="B3666" t="n">
+        <v>118</v>
+      </c>
+      <c r="C3666" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="3667">
+      <c r="A3667" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:00</t>
+        </is>
+      </c>
+      <c r="B3667" t="n">
+        <v>152</v>
+      </c>
+      <c r="C3667" t="n">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="3668">
+      <c r="A3668" t="inlineStr">
+        <is>
+          <t>2026-10-05 18:00</t>
+        </is>
+      </c>
+      <c r="B3668" t="n">
+        <v>168</v>
+      </c>
+      <c r="C3668" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="3669">
+      <c r="A3669" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+      <c r="B3669" t="n">
+        <v>172</v>
+      </c>
+      <c r="C3669" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3670">
+      <c r="A3670" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:00</t>
+        </is>
+      </c>
+      <c r="B3670" t="n">
+        <v>162</v>
+      </c>
+      <c r="C3670" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="3671">
+      <c r="A3671" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:00</t>
+        </is>
+      </c>
+      <c r="B3671" t="n">
+        <v>142</v>
+      </c>
+      <c r="C3671" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="3672">
+      <c r="A3672" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:00</t>
+        </is>
+      </c>
+      <c r="B3672" t="n">
+        <v>109</v>
+      </c>
+      <c r="C3672" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3673">
+      <c r="A3673" t="inlineStr">
+        <is>
+          <t>2026-10-05 23:00</t>
+        </is>
+      </c>
+      <c r="B3673" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3673" t="n">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3673"/>
+  <dimension ref="A1:C3697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48181,6 +48181,318 @@
         <v>53</v>
       </c>
     </row>
+    <row r="3674">
+      <c r="A3674" t="inlineStr">
+        <is>
+          <t>2026-10-06 00:00</t>
+        </is>
+      </c>
+      <c r="B3674" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3674" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="3675">
+      <c r="A3675" t="inlineStr">
+        <is>
+          <t>2026-10-06 01:00</t>
+        </is>
+      </c>
+      <c r="B3675" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3675" t="n">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="3676">
+      <c r="A3676" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:00</t>
+        </is>
+      </c>
+      <c r="B3676" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3676" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="3677">
+      <c r="A3677" t="inlineStr">
+        <is>
+          <t>2026-10-06 03:00</t>
+        </is>
+      </c>
+      <c r="B3677" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3677" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="3678">
+      <c r="A3678" t="inlineStr">
+        <is>
+          <t>2026-10-06 04:00</t>
+        </is>
+      </c>
+      <c r="B3678" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3678" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="3679">
+      <c r="A3679" t="inlineStr">
+        <is>
+          <t>2026-10-06 05:00</t>
+        </is>
+      </c>
+      <c r="B3679" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3679" t="n">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="3680">
+      <c r="A3680" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:00</t>
+        </is>
+      </c>
+      <c r="B3680" t="n">
+        <v>109</v>
+      </c>
+      <c r="C3680" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="3681">
+      <c r="A3681" t="inlineStr">
+        <is>
+          <t>2026-10-06 07:00</t>
+        </is>
+      </c>
+      <c r="B3681" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3681" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="3682">
+      <c r="A3682" t="inlineStr">
+        <is>
+          <t>2026-10-06 08:00</t>
+        </is>
+      </c>
+      <c r="B3682" t="n">
+        <v>109</v>
+      </c>
+      <c r="C3682" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3683">
+      <c r="A3683" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:00</t>
+        </is>
+      </c>
+      <c r="B3683" t="n">
+        <v>109</v>
+      </c>
+      <c r="C3683" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="3684">
+      <c r="A3684" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:00</t>
+        </is>
+      </c>
+      <c r="B3684" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3684" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="3685">
+      <c r="A3685" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00</t>
+        </is>
+      </c>
+      <c r="B3685" t="n">
+        <v>111</v>
+      </c>
+      <c r="C3685" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="3686">
+      <c r="A3686" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="B3686" t="n">
+        <v>111</v>
+      </c>
+      <c r="C3686" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3687">
+      <c r="A3687" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:00</t>
+        </is>
+      </c>
+      <c r="B3687" t="n">
+        <v>111</v>
+      </c>
+      <c r="C3687" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="3688">
+      <c r="A3688" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:00</t>
+        </is>
+      </c>
+      <c r="B3688" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3688" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00</t>
+        </is>
+      </c>
+      <c r="B3689" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3689" t="n">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="3690">
+      <c r="A3690" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:00</t>
+        </is>
+      </c>
+      <c r="B3690" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3690" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="3691">
+      <c r="A3691" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:00</t>
+        </is>
+      </c>
+      <c r="B3691" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3691" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="3692">
+      <c r="A3692" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:00</t>
+        </is>
+      </c>
+      <c r="B3692" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3692" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="3693">
+      <c r="A3693" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:00</t>
+        </is>
+      </c>
+      <c r="B3693" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3693" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="3694">
+      <c r="A3694" t="inlineStr">
+        <is>
+          <t>2026-10-06 20:00</t>
+        </is>
+      </c>
+      <c r="B3694" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3694" t="n">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="3695">
+      <c r="A3695" t="inlineStr">
+        <is>
+          <t>2026-10-06 21:00</t>
+        </is>
+      </c>
+      <c r="B3695" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3695" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="3696">
+      <c r="A3696" t="inlineStr">
+        <is>
+          <t>2026-10-06 22:00</t>
+        </is>
+      </c>
+      <c r="B3696" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3696" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="3697">
+      <c r="A3697" t="inlineStr">
+        <is>
+          <t>2026-10-06 23:00</t>
+        </is>
+      </c>
+      <c r="B3697" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3697" t="n">
+        <v>46.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3697"/>
+  <dimension ref="A1:C3721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48493,6 +48493,318 @@
         <v>46.9</v>
       </c>
     </row>
+    <row r="3698">
+      <c r="A3698" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00</t>
+        </is>
+      </c>
+      <c r="B3698" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3698" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="3699">
+      <c r="A3699" t="inlineStr">
+        <is>
+          <t>2026-10-07 01:00</t>
+        </is>
+      </c>
+      <c r="B3699" t="n">
+        <v>116</v>
+      </c>
+      <c r="C3699" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3700">
+      <c r="A3700" t="inlineStr">
+        <is>
+          <t>2026-10-07 02:00</t>
+        </is>
+      </c>
+      <c r="B3700" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3700" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="3701">
+      <c r="A3701" t="inlineStr">
+        <is>
+          <t>2026-10-07 03:00</t>
+        </is>
+      </c>
+      <c r="B3701" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3701" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3702">
+      <c r="A3702" t="inlineStr">
+        <is>
+          <t>2026-10-07 04:00</t>
+        </is>
+      </c>
+      <c r="B3702" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3702" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="3703">
+      <c r="A3703" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:00</t>
+        </is>
+      </c>
+      <c r="B3703" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3703" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="3704">
+      <c r="A3704" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="B3704" t="n">
+        <v>107</v>
+      </c>
+      <c r="C3704" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="3705">
+      <c r="A3705" t="inlineStr">
+        <is>
+          <t>2026-10-07 07:00</t>
+        </is>
+      </c>
+      <c r="B3705" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3705" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="3706">
+      <c r="A3706" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:00</t>
+        </is>
+      </c>
+      <c r="B3706" t="n">
+        <v>106</v>
+      </c>
+      <c r="C3706" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="3707">
+      <c r="A3707" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:00</t>
+        </is>
+      </c>
+      <c r="B3707" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3707" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="3708">
+      <c r="A3708" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:00</t>
+        </is>
+      </c>
+      <c r="B3708" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3708" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="3709">
+      <c r="A3709" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:00</t>
+        </is>
+      </c>
+      <c r="B3709" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3709" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="3710">
+      <c r="A3710" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:00</t>
+        </is>
+      </c>
+      <c r="B3710" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3710" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="3711">
+      <c r="A3711" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="B3711" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3711" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="3712">
+      <c r="A3712" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="B3712" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3712" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="3713">
+      <c r="A3713" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="B3713" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3713" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="3714">
+      <c r="A3714" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:00</t>
+        </is>
+      </c>
+      <c r="B3714" t="n">
+        <v>126</v>
+      </c>
+      <c r="C3714" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="3715">
+      <c r="A3715" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:00</t>
+        </is>
+      </c>
+      <c r="B3715" t="n">
+        <v>146</v>
+      </c>
+      <c r="C3715" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="3716">
+      <c r="A3716" t="inlineStr">
+        <is>
+          <t>2026-10-07 18:00</t>
+        </is>
+      </c>
+      <c r="B3716" t="n">
+        <v>151</v>
+      </c>
+      <c r="C3716" t="n">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="3717">
+      <c r="A3717" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:00</t>
+        </is>
+      </c>
+      <c r="B3717" t="n">
+        <v>144</v>
+      </c>
+      <c r="C3717" t="n">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="3718">
+      <c r="A3718" t="inlineStr">
+        <is>
+          <t>2026-10-07 20:00</t>
+        </is>
+      </c>
+      <c r="B3718" t="n">
+        <v>124</v>
+      </c>
+      <c r="C3718" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="3719">
+      <c r="A3719" t="inlineStr">
+        <is>
+          <t>2026-10-07 21:00</t>
+        </is>
+      </c>
+      <c r="B3719" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3719" t="n">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="3720">
+      <c r="A3720" t="inlineStr">
+        <is>
+          <t>2026-10-07 22:00</t>
+        </is>
+      </c>
+      <c r="B3720" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3720" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="3721">
+      <c r="A3721" t="inlineStr">
+        <is>
+          <t>2026-10-07 23:00</t>
+        </is>
+      </c>
+      <c r="B3721" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3721" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3721"/>
+  <dimension ref="A1:C3745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48805,6 +48805,318 @@
         <v>49.1</v>
       </c>
     </row>
+    <row r="3722">
+      <c r="A3722" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00</t>
+        </is>
+      </c>
+      <c r="B3722" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3722" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="3723">
+      <c r="A3723" t="inlineStr">
+        <is>
+          <t>2026-10-08 01:00</t>
+        </is>
+      </c>
+      <c r="B3723" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3723" t="n">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="3724">
+      <c r="A3724" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:00</t>
+        </is>
+      </c>
+      <c r="B3724" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3724" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="3725">
+      <c r="A3725" t="inlineStr">
+        <is>
+          <t>2026-10-08 03:00</t>
+        </is>
+      </c>
+      <c r="B3725" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3725" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="3726">
+      <c r="A3726" t="inlineStr">
+        <is>
+          <t>2026-10-08 04:00</t>
+        </is>
+      </c>
+      <c r="B3726" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3726" t="n">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="3727">
+      <c r="A3727" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:00</t>
+        </is>
+      </c>
+      <c r="B3727" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3727" t="n">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="3728">
+      <c r="A3728" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:00</t>
+        </is>
+      </c>
+      <c r="B3728" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3728" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="3729">
+      <c r="A3729" t="inlineStr">
+        <is>
+          <t>2026-10-08 07:00</t>
+        </is>
+      </c>
+      <c r="B3729" t="n">
+        <v>98</v>
+      </c>
+      <c r="C3729" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="3730">
+      <c r="A3730" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:00</t>
+        </is>
+      </c>
+      <c r="B3730" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3730" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3731">
+      <c r="A3731" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:00</t>
+        </is>
+      </c>
+      <c r="B3731" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3731" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="3732">
+      <c r="A3732" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:00</t>
+        </is>
+      </c>
+      <c r="B3732" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3732" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="3733">
+      <c r="A3733" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00</t>
+        </is>
+      </c>
+      <c r="B3733" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3733" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="3734">
+      <c r="A3734" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:00</t>
+        </is>
+      </c>
+      <c r="B3734" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3734" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="3735">
+      <c r="A3735" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:00</t>
+        </is>
+      </c>
+      <c r="B3735" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3735" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="3736">
+      <c r="A3736" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="B3736" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3736" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="3737">
+      <c r="A3737" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="B3737" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3737" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="3738">
+      <c r="A3738" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:00</t>
+        </is>
+      </c>
+      <c r="B3738" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3738" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="3739">
+      <c r="A3739" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:00</t>
+        </is>
+      </c>
+      <c r="B3739" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3739" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="3740">
+      <c r="A3740" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:00</t>
+        </is>
+      </c>
+      <c r="B3740" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3740" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="3741">
+      <c r="A3741" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:00</t>
+        </is>
+      </c>
+      <c r="B3741" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3741" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="3742">
+      <c r="A3742" t="inlineStr">
+        <is>
+          <t>2026-10-08 20:00</t>
+        </is>
+      </c>
+      <c r="B3742" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3742" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="3743">
+      <c r="A3743" t="inlineStr">
+        <is>
+          <t>2026-10-08 21:00</t>
+        </is>
+      </c>
+      <c r="B3743" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3743" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="3744">
+      <c r="A3744" t="inlineStr">
+        <is>
+          <t>2026-10-08 22:00</t>
+        </is>
+      </c>
+      <c r="B3744" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3744" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="3745">
+      <c r="A3745" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:00</t>
+        </is>
+      </c>
+      <c r="B3745" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3745" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3745"/>
+  <dimension ref="A1:C3769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49117,6 +49117,318 @@
         <v>17.6</v>
       </c>
     </row>
+    <row r="3746">
+      <c r="A3746" t="inlineStr">
+        <is>
+          <t>2026-10-09 00:00</t>
+        </is>
+      </c>
+      <c r="B3746" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3746" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="3747">
+      <c r="A3747" t="inlineStr">
+        <is>
+          <t>2026-10-09 01:00</t>
+        </is>
+      </c>
+      <c r="B3747" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3747" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="3748">
+      <c r="A3748" t="inlineStr">
+        <is>
+          <t>2026-10-09 02:00</t>
+        </is>
+      </c>
+      <c r="B3748" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3748" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="3749">
+      <c r="A3749" t="inlineStr">
+        <is>
+          <t>2026-10-09 03:00</t>
+        </is>
+      </c>
+      <c r="B3749" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3749" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="3750">
+      <c r="A3750" t="inlineStr">
+        <is>
+          <t>2026-10-09 04:00</t>
+        </is>
+      </c>
+      <c r="B3750" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3750" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="3751">
+      <c r="A3751" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:00</t>
+        </is>
+      </c>
+      <c r="B3751" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3751" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3752">
+      <c r="A3752" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:00</t>
+        </is>
+      </c>
+      <c r="B3752" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3752" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="3753">
+      <c r="A3753" t="inlineStr">
+        <is>
+          <t>2026-10-09 07:00</t>
+        </is>
+      </c>
+      <c r="B3753" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3753" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="3754">
+      <c r="A3754" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:00</t>
+        </is>
+      </c>
+      <c r="B3754" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3754" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="3755">
+      <c r="A3755" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:00</t>
+        </is>
+      </c>
+      <c r="B3755" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3755" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="3756">
+      <c r="A3756" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="B3756" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3756" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="3757">
+      <c r="A3757" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:00</t>
+        </is>
+      </c>
+      <c r="B3757" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3757" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="3758">
+      <c r="A3758" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:00</t>
+        </is>
+      </c>
+      <c r="B3758" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3758" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="3759">
+      <c r="A3759" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:00</t>
+        </is>
+      </c>
+      <c r="B3759" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3759" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3760">
+      <c r="A3760" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:00</t>
+        </is>
+      </c>
+      <c r="B3760" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3760" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3761">
+      <c r="A3761" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:00</t>
+        </is>
+      </c>
+      <c r="B3761" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3761" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="3762">
+      <c r="A3762" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:00</t>
+        </is>
+      </c>
+      <c r="B3762" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3762" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="3763">
+      <c r="A3763" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:00</t>
+        </is>
+      </c>
+      <c r="B3763" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3763" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="3764">
+      <c r="A3764" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:00</t>
+        </is>
+      </c>
+      <c r="B3764" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3764" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="3765">
+      <c r="A3765" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:00</t>
+        </is>
+      </c>
+      <c r="B3765" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3765" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="3766">
+      <c r="A3766" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:00</t>
+        </is>
+      </c>
+      <c r="B3766" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3766" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="3767">
+      <c r="A3767" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00</t>
+        </is>
+      </c>
+      <c r="B3767" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3767" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="3768">
+      <c r="A3768" t="inlineStr">
+        <is>
+          <t>2026-10-09 22:00</t>
+        </is>
+      </c>
+      <c r="B3768" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3768" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3769">
+      <c r="A3769" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:00</t>
+        </is>
+      </c>
+      <c r="B3769" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3769" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3769"/>
+  <dimension ref="A1:C3793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49429,6 +49429,318 @@
         <v>20.9</v>
       </c>
     </row>
+    <row r="3770">
+      <c r="A3770" t="inlineStr">
+        <is>
+          <t>2026-10-10 00:00</t>
+        </is>
+      </c>
+      <c r="B3770" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3770" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="3771">
+      <c r="A3771" t="inlineStr">
+        <is>
+          <t>2026-10-10 01:00</t>
+        </is>
+      </c>
+      <c r="B3771" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3771" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="3772">
+      <c r="A3772" t="inlineStr">
+        <is>
+          <t>2026-10-10 02:00</t>
+        </is>
+      </c>
+      <c r="B3772" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3772" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="3773">
+      <c r="A3773" t="inlineStr">
+        <is>
+          <t>2026-10-10 03:00</t>
+        </is>
+      </c>
+      <c r="B3773" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3773" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="3774">
+      <c r="A3774" t="inlineStr">
+        <is>
+          <t>2026-10-10 04:00</t>
+        </is>
+      </c>
+      <c r="B3774" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3774" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="3775">
+      <c r="A3775" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:00</t>
+        </is>
+      </c>
+      <c r="B3775" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3775" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="3776">
+      <c r="A3776" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:00</t>
+        </is>
+      </c>
+      <c r="B3776" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3776" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="3777">
+      <c r="A3777" t="inlineStr">
+        <is>
+          <t>2026-10-10 07:00</t>
+        </is>
+      </c>
+      <c r="B3777" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3777" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="3778">
+      <c r="A3778" t="inlineStr">
+        <is>
+          <t>2026-10-10 08:00</t>
+        </is>
+      </c>
+      <c r="B3778" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3778" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="3779">
+      <c r="A3779" t="inlineStr">
+        <is>
+          <t>2026-10-10 09:00</t>
+        </is>
+      </c>
+      <c r="B3779" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3779" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="3780">
+      <c r="A3780" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:00</t>
+        </is>
+      </c>
+      <c r="B3780" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3780" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="3781">
+      <c r="A3781" t="inlineStr">
+        <is>
+          <t>2026-10-10 11:00</t>
+        </is>
+      </c>
+      <c r="B3781" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3781" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3782">
+      <c r="A3782" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:00</t>
+        </is>
+      </c>
+      <c r="B3782" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3782" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3783">
+      <c r="A3783" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:00</t>
+        </is>
+      </c>
+      <c r="B3783" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3783" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="3784">
+      <c r="A3784" t="inlineStr">
+        <is>
+          <t>2026-10-10 14:00</t>
+        </is>
+      </c>
+      <c r="B3784" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3784" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="3785">
+      <c r="A3785" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:00</t>
+        </is>
+      </c>
+      <c r="B3785" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3785" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="3786">
+      <c r="A3786" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:00</t>
+        </is>
+      </c>
+      <c r="B3786" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3786" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3787">
+      <c r="A3787" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:00</t>
+        </is>
+      </c>
+      <c r="B3787" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3787" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="3788">
+      <c r="A3788" t="inlineStr">
+        <is>
+          <t>2026-10-10 18:00</t>
+        </is>
+      </c>
+      <c r="B3788" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3788" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="3789">
+      <c r="A3789" t="inlineStr">
+        <is>
+          <t>2026-10-10 19:00</t>
+        </is>
+      </c>
+      <c r="B3789" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3789" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3790">
+      <c r="A3790" t="inlineStr">
+        <is>
+          <t>2026-10-10 20:00</t>
+        </is>
+      </c>
+      <c r="B3790" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3790" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="3791">
+      <c r="A3791" t="inlineStr">
+        <is>
+          <t>2026-10-10 21:00</t>
+        </is>
+      </c>
+      <c r="B3791" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3791" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="3792">
+      <c r="A3792" t="inlineStr">
+        <is>
+          <t>2026-10-10 22:00</t>
+        </is>
+      </c>
+      <c r="B3792" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3792" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3793">
+      <c r="A3793" t="inlineStr">
+        <is>
+          <t>2026-10-10 23:00</t>
+        </is>
+      </c>
+      <c r="B3793" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3793" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3793"/>
+  <dimension ref="A1:C3817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49741,6 +49741,318 @@
         <v>20.9</v>
       </c>
     </row>
+    <row r="3794">
+      <c r="A3794" t="inlineStr">
+        <is>
+          <t>2026-10-11 00:00</t>
+        </is>
+      </c>
+      <c r="B3794" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3794" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="3795">
+      <c r="A3795" t="inlineStr">
+        <is>
+          <t>2026-10-11 01:00</t>
+        </is>
+      </c>
+      <c r="B3795" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3795" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="3796">
+      <c r="A3796" t="inlineStr">
+        <is>
+          <t>2026-10-11 02:00</t>
+        </is>
+      </c>
+      <c r="B3796" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3796" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3797">
+      <c r="A3797" t="inlineStr">
+        <is>
+          <t>2026-10-11 03:00</t>
+        </is>
+      </c>
+      <c r="B3797" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3797" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3798">
+      <c r="A3798" t="inlineStr">
+        <is>
+          <t>2026-10-11 04:00</t>
+        </is>
+      </c>
+      <c r="B3798" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3798" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="3799">
+      <c r="A3799" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:00</t>
+        </is>
+      </c>
+      <c r="B3799" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3799" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="3800">
+      <c r="A3800" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:00</t>
+        </is>
+      </c>
+      <c r="B3800" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3800" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="3801">
+      <c r="A3801" t="inlineStr">
+        <is>
+          <t>2026-10-11 07:00</t>
+        </is>
+      </c>
+      <c r="B3801" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3801" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="3802">
+      <c r="A3802" t="inlineStr">
+        <is>
+          <t>2026-10-11 08:00</t>
+        </is>
+      </c>
+      <c r="B3802" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3802" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="3803">
+      <c r="A3803" t="inlineStr">
+        <is>
+          <t>2026-10-11 09:00</t>
+        </is>
+      </c>
+      <c r="B3803" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3803" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="3804">
+      <c r="A3804" t="inlineStr">
+        <is>
+          <t>2026-10-11 10:00</t>
+        </is>
+      </c>
+      <c r="B3804" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3804" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="3805">
+      <c r="A3805" t="inlineStr">
+        <is>
+          <t>2026-10-11 11:00</t>
+        </is>
+      </c>
+      <c r="B3805" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3805" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="3806">
+      <c r="A3806" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:00</t>
+        </is>
+      </c>
+      <c r="B3806" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3806" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3807">
+      <c r="A3807" t="inlineStr">
+        <is>
+          <t>2026-10-11 13:00</t>
+        </is>
+      </c>
+      <c r="B3807" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3807" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3808">
+      <c r="A3808" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:00</t>
+        </is>
+      </c>
+      <c r="B3808" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3808" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="3809">
+      <c r="A3809" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:00</t>
+        </is>
+      </c>
+      <c r="B3809" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3809" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="3810">
+      <c r="A3810" t="inlineStr">
+        <is>
+          <t>2026-10-11 16:00</t>
+        </is>
+      </c>
+      <c r="B3810" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3810" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="3811">
+      <c r="A3811" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:00</t>
+        </is>
+      </c>
+      <c r="B3811" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3811" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3812">
+      <c r="A3812" t="inlineStr">
+        <is>
+          <t>2026-10-11 18:00</t>
+        </is>
+      </c>
+      <c r="B3812" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3812" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="3813">
+      <c r="A3813" t="inlineStr">
+        <is>
+          <t>2026-10-11 19:00</t>
+        </is>
+      </c>
+      <c r="B3813" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3813" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3814">
+      <c r="A3814" t="inlineStr">
+        <is>
+          <t>2026-10-11 20:00</t>
+        </is>
+      </c>
+      <c r="B3814" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3814" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="3815">
+      <c r="A3815" t="inlineStr">
+        <is>
+          <t>2026-10-11 21:00</t>
+        </is>
+      </c>
+      <c r="B3815" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3815" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="3816">
+      <c r="A3816" t="inlineStr">
+        <is>
+          <t>2026-10-11 22:00</t>
+        </is>
+      </c>
+      <c r="B3816" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3816" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="3817">
+      <c r="A3817" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:00</t>
+        </is>
+      </c>
+      <c r="B3817" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3817" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3817"/>
+  <dimension ref="A1:C3841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50053,6 +50053,318 @@
         <v>27.5</v>
       </c>
     </row>
+    <row r="3818">
+      <c r="A3818" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00</t>
+        </is>
+      </c>
+      <c r="B3818" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3818" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="3819">
+      <c r="A3819" t="inlineStr">
+        <is>
+          <t>2026-10-12 01:00</t>
+        </is>
+      </c>
+      <c r="B3819" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3819" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="3820">
+      <c r="A3820" t="inlineStr">
+        <is>
+          <t>2026-10-12 02:00</t>
+        </is>
+      </c>
+      <c r="B3820" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3820" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="3821">
+      <c r="A3821" t="inlineStr">
+        <is>
+          <t>2026-10-12 03:00</t>
+        </is>
+      </c>
+      <c r="B3821" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3821" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="3822">
+      <c r="A3822" t="inlineStr">
+        <is>
+          <t>2026-10-12 04:00</t>
+        </is>
+      </c>
+      <c r="B3822" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3822" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="3823">
+      <c r="A3823" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:00</t>
+        </is>
+      </c>
+      <c r="B3823" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3823" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="3824">
+      <c r="A3824" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:00</t>
+        </is>
+      </c>
+      <c r="B3824" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3824" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="3825">
+      <c r="A3825" t="inlineStr">
+        <is>
+          <t>2026-10-12 07:00</t>
+        </is>
+      </c>
+      <c r="B3825" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3825" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="3826">
+      <c r="A3826" t="inlineStr">
+        <is>
+          <t>2026-10-12 08:00</t>
+        </is>
+      </c>
+      <c r="B3826" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3826" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="3827">
+      <c r="A3827" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:00</t>
+        </is>
+      </c>
+      <c r="B3827" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3827" t="n">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="3828">
+      <c r="A3828" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:00</t>
+        </is>
+      </c>
+      <c r="B3828" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3828" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="3829">
+      <c r="A3829" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:00</t>
+        </is>
+      </c>
+      <c r="B3829" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3829" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3830">
+      <c r="A3830" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:00</t>
+        </is>
+      </c>
+      <c r="B3830" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3830" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3831">
+      <c r="A3831" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:00</t>
+        </is>
+      </c>
+      <c r="B3831" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3831" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="3832">
+      <c r="A3832" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:00</t>
+        </is>
+      </c>
+      <c r="B3832" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3832" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="3833">
+      <c r="A3833" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:00</t>
+        </is>
+      </c>
+      <c r="B3833" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3833" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="3834">
+      <c r="A3834" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:00</t>
+        </is>
+      </c>
+      <c r="B3834" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3834" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:00</t>
+        </is>
+      </c>
+      <c r="B3835" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3835" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:00</t>
+        </is>
+      </c>
+      <c r="B3836" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3836" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3837">
+      <c r="A3837" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:00</t>
+        </is>
+      </c>
+      <c r="B3837" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3837" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="3838">
+      <c r="A3838" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:00</t>
+        </is>
+      </c>
+      <c r="B3838" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3838" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="3839">
+      <c r="A3839" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00</t>
+        </is>
+      </c>
+      <c r="B3839" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3839" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="3840">
+      <c r="A3840" t="inlineStr">
+        <is>
+          <t>2026-10-12 22:00</t>
+        </is>
+      </c>
+      <c r="B3840" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3840" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="3841">
+      <c r="A3841" t="inlineStr">
+        <is>
+          <t>2026-10-12 23:00</t>
+        </is>
+      </c>
+      <c r="B3841" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3841" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3841"/>
+  <dimension ref="A1:C3865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50365,6 +50365,318 @@
         <v>39.6</v>
       </c>
     </row>
+    <row r="3842">
+      <c r="A3842" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00</t>
+        </is>
+      </c>
+      <c r="B3842" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3842" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="3843">
+      <c r="A3843" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:00</t>
+        </is>
+      </c>
+      <c r="B3843" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3843" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3844">
+      <c r="A3844" t="inlineStr">
+        <is>
+          <t>2026-10-13 02:00</t>
+        </is>
+      </c>
+      <c r="B3844" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3844" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="3845">
+      <c r="A3845" t="inlineStr">
+        <is>
+          <t>2026-10-13 03:00</t>
+        </is>
+      </c>
+      <c r="B3845" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3845" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="3846">
+      <c r="A3846" t="inlineStr">
+        <is>
+          <t>2026-10-13 04:00</t>
+        </is>
+      </c>
+      <c r="B3846" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3846" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="3847">
+      <c r="A3847" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:00</t>
+        </is>
+      </c>
+      <c r="B3847" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3847" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="3848">
+      <c r="A3848" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:00</t>
+        </is>
+      </c>
+      <c r="B3848" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3848" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="3849">
+      <c r="A3849" t="inlineStr">
+        <is>
+          <t>2026-10-13 07:00</t>
+        </is>
+      </c>
+      <c r="B3849" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3849" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="3850">
+      <c r="A3850" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:00</t>
+        </is>
+      </c>
+      <c r="B3850" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3850" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="3851">
+      <c r="A3851" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:00</t>
+        </is>
+      </c>
+      <c r="B3851" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3851" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="3852">
+      <c r="A3852" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="B3852" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3852" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="3853">
+      <c r="A3853" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:00</t>
+        </is>
+      </c>
+      <c r="B3853" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3853" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="3854">
+      <c r="A3854" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:00</t>
+        </is>
+      </c>
+      <c r="B3854" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3854" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="3855">
+      <c r="A3855" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:00</t>
+        </is>
+      </c>
+      <c r="B3855" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3855" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="3856">
+      <c r="A3856" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:00</t>
+        </is>
+      </c>
+      <c r="B3856" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3856" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="3857">
+      <c r="A3857" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:00</t>
+        </is>
+      </c>
+      <c r="B3857" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3857" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="3858">
+      <c r="A3858" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:00</t>
+        </is>
+      </c>
+      <c r="B3858" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3858" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="3859">
+      <c r="A3859" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:00</t>
+        </is>
+      </c>
+      <c r="B3859" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3859" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3860">
+      <c r="A3860" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:00</t>
+        </is>
+      </c>
+      <c r="B3860" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3860" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="3861">
+      <c r="A3861" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:00</t>
+        </is>
+      </c>
+      <c r="B3861" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3861" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="3862">
+      <c r="A3862" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:00</t>
+        </is>
+      </c>
+      <c r="B3862" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3862" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="3863">
+      <c r="A3863" t="inlineStr">
+        <is>
+          <t>2026-10-13 21:00</t>
+        </is>
+      </c>
+      <c r="B3863" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3863" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="3864">
+      <c r="A3864" t="inlineStr">
+        <is>
+          <t>2026-10-13 22:00</t>
+        </is>
+      </c>
+      <c r="B3864" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3864" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="3865">
+      <c r="A3865" t="inlineStr">
+        <is>
+          <t>2026-10-13 23:00</t>
+        </is>
+      </c>
+      <c r="B3865" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3865" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3865"/>
+  <dimension ref="A1:C3889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50677,6 +50677,318 @@
         <v>28.5</v>
       </c>
     </row>
+    <row r="3866">
+      <c r="A3866" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:00</t>
+        </is>
+      </c>
+      <c r="B3866" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3866" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3867">
+      <c r="A3867" t="inlineStr">
+        <is>
+          <t>2026-10-14 01:00</t>
+        </is>
+      </c>
+      <c r="B3867" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3867" t="n">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="3868">
+      <c r="A3868" t="inlineStr">
+        <is>
+          <t>2026-10-14 02:00</t>
+        </is>
+      </c>
+      <c r="B3868" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3868" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="3869">
+      <c r="A3869" t="inlineStr">
+        <is>
+          <t>2026-10-14 03:00</t>
+        </is>
+      </c>
+      <c r="B3869" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3869" t="n">
+        <v>37.7</v>
+      </c>
+    </row>
+    <row r="3870">
+      <c r="A3870" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:00</t>
+        </is>
+      </c>
+      <c r="B3870" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3870" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="3871">
+      <c r="A3871" t="inlineStr">
+        <is>
+          <t>2026-10-14 05:00</t>
+        </is>
+      </c>
+      <c r="B3871" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3871" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="3872">
+      <c r="A3872" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:00</t>
+        </is>
+      </c>
+      <c r="B3872" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3872" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="3873">
+      <c r="A3873" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:00</t>
+        </is>
+      </c>
+      <c r="B3873" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3873" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="3874">
+      <c r="A3874" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:00</t>
+        </is>
+      </c>
+      <c r="B3874" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3874" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="3875">
+      <c r="A3875" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:00</t>
+        </is>
+      </c>
+      <c r="B3875" t="n">
+        <v>79</v>
+      </c>
+      <c r="C3875" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="3876">
+      <c r="A3876" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="B3876" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3876" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="3877">
+      <c r="A3877" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:00</t>
+        </is>
+      </c>
+      <c r="B3877" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3877" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="3878">
+      <c r="A3878" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="B3878" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3878" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="3879">
+      <c r="A3879" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:00</t>
+        </is>
+      </c>
+      <c r="B3879" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3879" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="3880">
+      <c r="A3880" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:00</t>
+        </is>
+      </c>
+      <c r="B3880" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3880" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="3881">
+      <c r="A3881" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="B3881" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3881" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3882">
+      <c r="A3882" t="inlineStr">
+        <is>
+          <t>2026-10-14 16:00</t>
+        </is>
+      </c>
+      <c r="B3882" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3882" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="3883">
+      <c r="A3883" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:00</t>
+        </is>
+      </c>
+      <c r="B3883" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3883" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="3884">
+      <c r="A3884" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:00</t>
+        </is>
+      </c>
+      <c r="B3884" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3884" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="3885">
+      <c r="A3885" t="inlineStr">
+        <is>
+          <t>2026-10-14 19:00</t>
+        </is>
+      </c>
+      <c r="B3885" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3885" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3886">
+      <c r="A3886" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:00</t>
+        </is>
+      </c>
+      <c r="B3886" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3886" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="3887">
+      <c r="A3887" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:00</t>
+        </is>
+      </c>
+      <c r="B3887" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3887" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3888">
+      <c r="A3888" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:00</t>
+        </is>
+      </c>
+      <c r="B3888" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3888" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="3889">
+      <c r="A3889" t="inlineStr">
+        <is>
+          <t>2026-10-14 23:00</t>
+        </is>
+      </c>
+      <c r="B3889" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3889" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3889"/>
+  <dimension ref="A1:C3913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50989,6 +50989,318 @@
         <v>42.7</v>
       </c>
     </row>
+    <row r="3890">
+      <c r="A3890" t="inlineStr">
+        <is>
+          <t>2026-10-15 00:00</t>
+        </is>
+      </c>
+      <c r="B3890" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3890" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="3891">
+      <c r="A3891" t="inlineStr">
+        <is>
+          <t>2026-10-15 01:00</t>
+        </is>
+      </c>
+      <c r="B3891" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3891" t="n">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="3892">
+      <c r="A3892" t="inlineStr">
+        <is>
+          <t>2026-10-15 02:00</t>
+        </is>
+      </c>
+      <c r="B3892" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3892" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="3893">
+      <c r="A3893" t="inlineStr">
+        <is>
+          <t>2026-10-15 03:00</t>
+        </is>
+      </c>
+      <c r="B3893" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3893" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="3894">
+      <c r="A3894" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:00</t>
+        </is>
+      </c>
+      <c r="B3894" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3894" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="3895">
+      <c r="A3895" t="inlineStr">
+        <is>
+          <t>2026-10-15 05:00</t>
+        </is>
+      </c>
+      <c r="B3895" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3895" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="3896">
+      <c r="A3896" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:00</t>
+        </is>
+      </c>
+      <c r="B3896" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3896" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="3897">
+      <c r="A3897" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:00</t>
+        </is>
+      </c>
+      <c r="B3897" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3897" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3898">
+      <c r="A3898" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:00</t>
+        </is>
+      </c>
+      <c r="B3898" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3898" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="3899">
+      <c r="A3899" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:00</t>
+        </is>
+      </c>
+      <c r="B3899" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3899" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="3900">
+      <c r="A3900" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="B3900" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3900" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="3901">
+      <c r="A3901" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:00</t>
+        </is>
+      </c>
+      <c r="B3901" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3901" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:00</t>
+        </is>
+      </c>
+      <c r="B3902" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3902" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="3903">
+      <c r="A3903" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:00</t>
+        </is>
+      </c>
+      <c r="B3903" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3903" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="3904">
+      <c r="A3904" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:00</t>
+        </is>
+      </c>
+      <c r="B3904" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3904" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:00</t>
+        </is>
+      </c>
+      <c r="B3905" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3905" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:00</t>
+        </is>
+      </c>
+      <c r="B3906" t="n">
+        <v>93</v>
+      </c>
+      <c r="C3906" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="3907">
+      <c r="A3907" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:00</t>
+        </is>
+      </c>
+      <c r="B3907" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3907" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="3908">
+      <c r="A3908" t="inlineStr">
+        <is>
+          <t>2026-10-15 18:00</t>
+        </is>
+      </c>
+      <c r="B3908" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3908" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3909">
+      <c r="A3909" t="inlineStr">
+        <is>
+          <t>2026-10-15 19:00</t>
+        </is>
+      </c>
+      <c r="B3909" t="n">
+        <v>97</v>
+      </c>
+      <c r="C3909" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="3910">
+      <c r="A3910" t="inlineStr">
+        <is>
+          <t>2026-10-15 20:00</t>
+        </is>
+      </c>
+      <c r="B3910" t="n">
+        <v>99</v>
+      </c>
+      <c r="C3910" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="3911">
+      <c r="A3911" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:00</t>
+        </is>
+      </c>
+      <c r="B3911" t="n">
+        <v>102</v>
+      </c>
+      <c r="C3911" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="3912">
+      <c r="A3912" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:00</t>
+        </is>
+      </c>
+      <c r="B3912" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3912" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="3913">
+      <c r="A3913" t="inlineStr">
+        <is>
+          <t>2026-10-15 23:00</t>
+        </is>
+      </c>
+      <c r="B3913" t="n">
+        <v>107</v>
+      </c>
+      <c r="C3913" t="n">
+        <v>65.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3913"/>
+  <dimension ref="A1:C3937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51301,6 +51301,318 @@
         <v>65.2</v>
       </c>
     </row>
+    <row r="3914">
+      <c r="A3914" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:00</t>
+        </is>
+      </c>
+      <c r="B3914" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3914" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="3915">
+      <c r="A3915" t="inlineStr">
+        <is>
+          <t>2026-10-16 01:00</t>
+        </is>
+      </c>
+      <c r="B3915" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3915" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="3916">
+      <c r="A3916" t="inlineStr">
+        <is>
+          <t>2026-10-16 02:00</t>
+        </is>
+      </c>
+      <c r="B3916" t="n">
+        <v>115</v>
+      </c>
+      <c r="C3916" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="3917">
+      <c r="A3917" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:00</t>
+        </is>
+      </c>
+      <c r="B3917" t="n">
+        <v>117</v>
+      </c>
+      <c r="C3917" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="3918">
+      <c r="A3918" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:00</t>
+        </is>
+      </c>
+      <c r="B3918" t="n">
+        <v>118</v>
+      </c>
+      <c r="C3918" t="n">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="3919">
+      <c r="A3919" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:00</t>
+        </is>
+      </c>
+      <c r="B3919" t="n">
+        <v>119</v>
+      </c>
+      <c r="C3919" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="3920">
+      <c r="A3920" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="B3920" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3920" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3921">
+      <c r="A3921" t="inlineStr">
+        <is>
+          <t>2026-10-16 07:00</t>
+        </is>
+      </c>
+      <c r="B3921" t="n">
+        <v>121</v>
+      </c>
+      <c r="C3921" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="3922">
+      <c r="A3922" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:00</t>
+        </is>
+      </c>
+      <c r="B3922" t="n">
+        <v>124</v>
+      </c>
+      <c r="C3922" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="3923">
+      <c r="A3923" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:00</t>
+        </is>
+      </c>
+      <c r="B3923" t="n">
+        <v>126</v>
+      </c>
+      <c r="C3923" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="3924">
+      <c r="A3924" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00</t>
+        </is>
+      </c>
+      <c r="B3924" t="n">
+        <v>126</v>
+      </c>
+      <c r="C3924" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="3925">
+      <c r="A3925" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00</t>
+        </is>
+      </c>
+      <c r="B3925" t="n">
+        <v>127</v>
+      </c>
+      <c r="C3925" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="3926">
+      <c r="A3926" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:00</t>
+        </is>
+      </c>
+      <c r="B3926" t="n">
+        <v>127</v>
+      </c>
+      <c r="C3926" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="3927">
+      <c r="A3927" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:00</t>
+        </is>
+      </c>
+      <c r="B3927" t="n">
+        <v>128</v>
+      </c>
+      <c r="C3927" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="3928">
+      <c r="A3928" t="inlineStr">
+        <is>
+          <t>2026-10-16 14:00</t>
+        </is>
+      </c>
+      <c r="B3928" t="n">
+        <v>127</v>
+      </c>
+      <c r="C3928" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="3929">
+      <c r="A3929" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:00</t>
+        </is>
+      </c>
+      <c r="B3929" t="n">
+        <v>127</v>
+      </c>
+      <c r="C3929" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="3930">
+      <c r="A3930" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:00</t>
+        </is>
+      </c>
+      <c r="B3930" t="n">
+        <v>127</v>
+      </c>
+      <c r="C3930" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="3931">
+      <c r="A3931" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:00</t>
+        </is>
+      </c>
+      <c r="B3931" t="n">
+        <v>126</v>
+      </c>
+      <c r="C3931" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="3932">
+      <c r="A3932" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:00</t>
+        </is>
+      </c>
+      <c r="B3932" t="n">
+        <v>124</v>
+      </c>
+      <c r="C3932" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="3933">
+      <c r="A3933" t="inlineStr">
+        <is>
+          <t>2026-10-16 19:00</t>
+        </is>
+      </c>
+      <c r="B3933" t="n">
+        <v>121</v>
+      </c>
+      <c r="C3933" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="3934">
+      <c r="A3934" t="inlineStr">
+        <is>
+          <t>2026-10-16 20:00</t>
+        </is>
+      </c>
+      <c r="B3934" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3934" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="3935">
+      <c r="A3935" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:00</t>
+        </is>
+      </c>
+      <c r="B3935" t="n">
+        <v>117</v>
+      </c>
+      <c r="C3935" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3936">
+      <c r="A3936" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:00</t>
+        </is>
+      </c>
+      <c r="B3936" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3936" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="3937">
+      <c r="A3937" t="inlineStr">
+        <is>
+          <t>2026-10-16 23:00</t>
+        </is>
+      </c>
+      <c r="B3937" t="n">
+        <v>109</v>
+      </c>
+      <c r="C3937" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3937"/>
+  <dimension ref="A1:C3961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51613,6 +51613,318 @@
         <v>21.2</v>
       </c>
     </row>
+    <row r="3938">
+      <c r="A3938" t="inlineStr">
+        <is>
+          <t>2026-10-17 00:00</t>
+        </is>
+      </c>
+      <c r="B3938" t="n">
+        <v>105</v>
+      </c>
+      <c r="C3938" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3939">
+      <c r="A3939" t="inlineStr">
+        <is>
+          <t>2026-10-17 01:00</t>
+        </is>
+      </c>
+      <c r="B3939" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3939" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3940">
+      <c r="A3940" t="inlineStr">
+        <is>
+          <t>2026-10-17 02:00</t>
+        </is>
+      </c>
+      <c r="B3940" t="n">
+        <v>96</v>
+      </c>
+      <c r="C3940" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3941">
+      <c r="A3941" t="inlineStr">
+        <is>
+          <t>2026-10-17 03:00</t>
+        </is>
+      </c>
+      <c r="B3941" t="n">
+        <v>92</v>
+      </c>
+      <c r="C3941" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="3942">
+      <c r="A3942" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:00</t>
+        </is>
+      </c>
+      <c r="B3942" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3942" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3943">
+      <c r="A3943" t="inlineStr">
+        <is>
+          <t>2026-10-17 05:00</t>
+        </is>
+      </c>
+      <c r="B3943" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3943" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="3944">
+      <c r="A3944" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:00</t>
+        </is>
+      </c>
+      <c r="B3944" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3944" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3945">
+      <c r="A3945" t="inlineStr">
+        <is>
+          <t>2026-10-17 07:00</t>
+        </is>
+      </c>
+      <c r="B3945" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3945" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="3946">
+      <c r="A3946" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:00</t>
+        </is>
+      </c>
+      <c r="B3946" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3946" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="3947">
+      <c r="A3947" t="inlineStr">
+        <is>
+          <t>2026-10-17 09:00</t>
+        </is>
+      </c>
+      <c r="B3947" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3947" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="3948">
+      <c r="A3948" t="inlineStr">
+        <is>
+          <t>2026-10-17 10:00</t>
+        </is>
+      </c>
+      <c r="B3948" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3948" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="3949">
+      <c r="A3949" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:00</t>
+        </is>
+      </c>
+      <c r="B3949" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3949" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="3950">
+      <c r="A3950" t="inlineStr">
+        <is>
+          <t>2026-10-17 12:00</t>
+        </is>
+      </c>
+      <c r="B3950" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3950" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="3951">
+      <c r="A3951" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:00</t>
+        </is>
+      </c>
+      <c r="B3951" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3951" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3952">
+      <c r="A3952" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:00</t>
+        </is>
+      </c>
+      <c r="B3952" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3952" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="3953">
+      <c r="A3953" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:00</t>
+        </is>
+      </c>
+      <c r="B3953" t="n">
+        <v>74</v>
+      </c>
+      <c r="C3953" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="3954">
+      <c r="A3954" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:00</t>
+        </is>
+      </c>
+      <c r="B3954" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3954" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="3955">
+      <c r="A3955" t="inlineStr">
+        <is>
+          <t>2026-10-17 17:00</t>
+        </is>
+      </c>
+      <c r="B3955" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3955" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="3956">
+      <c r="A3956" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:00</t>
+        </is>
+      </c>
+      <c r="B3956" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3956" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="3957">
+      <c r="A3957" t="inlineStr">
+        <is>
+          <t>2026-10-17 19:00</t>
+        </is>
+      </c>
+      <c r="B3957" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3957" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="3958">
+      <c r="A3958" t="inlineStr">
+        <is>
+          <t>2026-10-17 20:00</t>
+        </is>
+      </c>
+      <c r="B3958" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3958" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="3959">
+      <c r="A3959" t="inlineStr">
+        <is>
+          <t>2026-10-17 21:00</t>
+        </is>
+      </c>
+      <c r="B3959" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3959" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="3960">
+      <c r="A3960" t="inlineStr">
+        <is>
+          <t>2026-10-17 22:00</t>
+        </is>
+      </c>
+      <c r="B3960" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3960" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="3961">
+      <c r="A3961" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:00</t>
+        </is>
+      </c>
+      <c r="B3961" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3961" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3961"/>
+  <dimension ref="A1:C3985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51925,6 +51925,318 @@
         <v>18.6</v>
       </c>
     </row>
+    <row r="3962">
+      <c r="A3962" t="inlineStr">
+        <is>
+          <t>2026-10-18 00:00</t>
+        </is>
+      </c>
+      <c r="B3962" t="n">
+        <v>69</v>
+      </c>
+      <c r="C3962" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="3963">
+      <c r="A3963" t="inlineStr">
+        <is>
+          <t>2026-10-18 01:00</t>
+        </is>
+      </c>
+      <c r="B3963" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3963" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="3964">
+      <c r="A3964" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:00</t>
+        </is>
+      </c>
+      <c r="B3964" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3964" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="3965">
+      <c r="A3965" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:00</t>
+        </is>
+      </c>
+      <c r="B3965" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3965" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="3966">
+      <c r="A3966" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:00</t>
+        </is>
+      </c>
+      <c r="B3966" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3966" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="3967">
+      <c r="A3967" t="inlineStr">
+        <is>
+          <t>2026-10-18 05:00</t>
+        </is>
+      </c>
+      <c r="B3967" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3967" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="3968">
+      <c r="A3968" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:00</t>
+        </is>
+      </c>
+      <c r="B3968" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3968" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3969">
+      <c r="A3969" t="inlineStr">
+        <is>
+          <t>2026-10-18 07:00</t>
+        </is>
+      </c>
+      <c r="B3969" t="n">
+        <v>68</v>
+      </c>
+      <c r="C3969" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="3970">
+      <c r="A3970" t="inlineStr">
+        <is>
+          <t>2026-10-18 08:00</t>
+        </is>
+      </c>
+      <c r="B3970" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3970" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="3971">
+      <c r="A3971" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:00</t>
+        </is>
+      </c>
+      <c r="B3971" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3971" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="3972">
+      <c r="A3972" t="inlineStr">
+        <is>
+          <t>2026-10-18 10:00</t>
+        </is>
+      </c>
+      <c r="B3972" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3972" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="3973">
+      <c r="A3973" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:00</t>
+        </is>
+      </c>
+      <c r="B3973" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3973" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="3974">
+      <c r="A3974" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:00</t>
+        </is>
+      </c>
+      <c r="B3974" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3974" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="3975">
+      <c r="A3975" t="inlineStr">
+        <is>
+          <t>2026-10-18 13:00</t>
+        </is>
+      </c>
+      <c r="B3975" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3975" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="3976">
+      <c r="A3976" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:00</t>
+        </is>
+      </c>
+      <c r="B3976" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3976" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="3977">
+      <c r="A3977" t="inlineStr">
+        <is>
+          <t>2026-10-18 15:00</t>
+        </is>
+      </c>
+      <c r="B3977" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3977" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="3978">
+      <c r="A3978" t="inlineStr">
+        <is>
+          <t>2026-10-18 16:00</t>
+        </is>
+      </c>
+      <c r="B3978" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3978" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="3979">
+      <c r="A3979" t="inlineStr">
+        <is>
+          <t>2026-10-18 17:00</t>
+        </is>
+      </c>
+      <c r="B3979" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3979" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="3980">
+      <c r="A3980" t="inlineStr">
+        <is>
+          <t>2026-10-18 18:00</t>
+        </is>
+      </c>
+      <c r="B3980" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3980" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="3981">
+      <c r="A3981" t="inlineStr">
+        <is>
+          <t>2026-10-18 19:00</t>
+        </is>
+      </c>
+      <c r="B3981" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3981" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="3982">
+      <c r="A3982" t="inlineStr">
+        <is>
+          <t>2026-10-18 20:00</t>
+        </is>
+      </c>
+      <c r="B3982" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3982" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="3983">
+      <c r="A3983" t="inlineStr">
+        <is>
+          <t>2026-10-18 21:00</t>
+        </is>
+      </c>
+      <c r="B3983" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3983" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="3984">
+      <c r="A3984" t="inlineStr">
+        <is>
+          <t>2026-10-18 22:00</t>
+        </is>
+      </c>
+      <c r="B3984" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3984" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="3985">
+      <c r="A3985" t="inlineStr">
+        <is>
+          <t>2026-10-18 23:00</t>
+        </is>
+      </c>
+      <c r="B3985" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3985" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3985"/>
+  <dimension ref="A1:C4009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52237,6 +52237,318 @@
         <v>13.4</v>
       </c>
     </row>
+    <row r="3986">
+      <c r="A3986" t="inlineStr">
+        <is>
+          <t>2026-10-19 00:00</t>
+        </is>
+      </c>
+      <c r="B3986" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3986" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="3987">
+      <c r="A3987" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00</t>
+        </is>
+      </c>
+      <c r="B3987" t="n">
+        <v>59</v>
+      </c>
+      <c r="C3987" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="3988">
+      <c r="A3988" t="inlineStr">
+        <is>
+          <t>2026-10-19 02:00</t>
+        </is>
+      </c>
+      <c r="B3988" t="n">
+        <v>58</v>
+      </c>
+      <c r="C3988" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="3989">
+      <c r="A3989" t="inlineStr">
+        <is>
+          <t>2026-10-19 03:00</t>
+        </is>
+      </c>
+      <c r="B3989" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3989" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="3990">
+      <c r="A3990" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00</t>
+        </is>
+      </c>
+      <c r="B3990" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3990" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="3991">
+      <c r="A3991" t="inlineStr">
+        <is>
+          <t>2026-10-19 05:00</t>
+        </is>
+      </c>
+      <c r="B3991" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3991" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="3992">
+      <c r="A3992" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00</t>
+        </is>
+      </c>
+      <c r="B3992" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3992" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3993">
+      <c r="A3993" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:00</t>
+        </is>
+      </c>
+      <c r="B3993" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3993" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="3994">
+      <c r="A3994" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:00</t>
+        </is>
+      </c>
+      <c r="B3994" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3994" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="3995">
+      <c r="A3995" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:00</t>
+        </is>
+      </c>
+      <c r="B3995" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3995" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="3996">
+      <c r="A3996" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:00</t>
+        </is>
+      </c>
+      <c r="B3996" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3996" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="3997">
+      <c r="A3997" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:00</t>
+        </is>
+      </c>
+      <c r="B3997" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3997" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="3998">
+      <c r="A3998" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:00</t>
+        </is>
+      </c>
+      <c r="B3998" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3998" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="3999">
+      <c r="A3999" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:00</t>
+        </is>
+      </c>
+      <c r="B3999" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3999" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="4000">
+      <c r="A4000" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:00</t>
+        </is>
+      </c>
+      <c r="B4000" t="n">
+        <v>57</v>
+      </c>
+      <c r="C4000" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="4001">
+      <c r="A4001" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:00</t>
+        </is>
+      </c>
+      <c r="B4001" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4001" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="4002">
+      <c r="A4002" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:00</t>
+        </is>
+      </c>
+      <c r="B4002" t="n">
+        <v>59</v>
+      </c>
+      <c r="C4002" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="4003">
+      <c r="A4003" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:00</t>
+        </is>
+      </c>
+      <c r="B4003" t="n">
+        <v>59</v>
+      </c>
+      <c r="C4003" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="4004">
+      <c r="A4004" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:00</t>
+        </is>
+      </c>
+      <c r="B4004" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4004" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="4005">
+      <c r="A4005" t="inlineStr">
+        <is>
+          <t>2026-10-19 19:00</t>
+        </is>
+      </c>
+      <c r="B4005" t="n">
+        <v>61</v>
+      </c>
+      <c r="C4005" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="4006">
+      <c r="A4006" t="inlineStr">
+        <is>
+          <t>2026-10-19 20:00</t>
+        </is>
+      </c>
+      <c r="B4006" t="n">
+        <v>61</v>
+      </c>
+      <c r="C4006" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4007">
+      <c r="A4007" t="inlineStr">
+        <is>
+          <t>2026-10-19 21:00</t>
+        </is>
+      </c>
+      <c r="B4007" t="n">
+        <v>61</v>
+      </c>
+      <c r="C4007" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="4008">
+      <c r="A4008" t="inlineStr">
+        <is>
+          <t>2026-10-19 22:00</t>
+        </is>
+      </c>
+      <c r="B4008" t="n">
+        <v>62</v>
+      </c>
+      <c r="C4008" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="4009">
+      <c r="A4009" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:00</t>
+        </is>
+      </c>
+      <c r="B4009" t="n">
+        <v>62</v>
+      </c>
+      <c r="C4009" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4009"/>
+  <dimension ref="A1:C4033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52549,6 +52549,318 @@
         <v>22.1</v>
       </c>
     </row>
+    <row r="4010">
+      <c r="A4010" t="inlineStr">
+        <is>
+          <t>2026-10-20 00:00</t>
+        </is>
+      </c>
+      <c r="B4010" t="n">
+        <v>63</v>
+      </c>
+      <c r="C4010" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="4011">
+      <c r="A4011" t="inlineStr">
+        <is>
+          <t>2026-10-20 01:00</t>
+        </is>
+      </c>
+      <c r="B4011" t="n">
+        <v>64</v>
+      </c>
+      <c r="C4011" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="4012">
+      <c r="A4012" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00</t>
+        </is>
+      </c>
+      <c r="B4012" t="n">
+        <v>65</v>
+      </c>
+      <c r="C4012" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="4013">
+      <c r="A4013" t="inlineStr">
+        <is>
+          <t>2026-10-20 03:00</t>
+        </is>
+      </c>
+      <c r="B4013" t="n">
+        <v>66</v>
+      </c>
+      <c r="C4013" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="4014">
+      <c r="A4014" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:00</t>
+        </is>
+      </c>
+      <c r="B4014" t="n">
+        <v>67</v>
+      </c>
+      <c r="C4014" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="4015">
+      <c r="A4015" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:00</t>
+        </is>
+      </c>
+      <c r="B4015" t="n">
+        <v>68</v>
+      </c>
+      <c r="C4015" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="4016">
+      <c r="A4016" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:00</t>
+        </is>
+      </c>
+      <c r="B4016" t="n">
+        <v>69</v>
+      </c>
+      <c r="C4016" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4017">
+      <c r="A4017" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:00</t>
+        </is>
+      </c>
+      <c r="B4017" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4017" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="4018">
+      <c r="A4018" t="inlineStr">
+        <is>
+          <t>2026-10-20 08:00</t>
+        </is>
+      </c>
+      <c r="B4018" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4018" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="4019">
+      <c r="A4019" t="inlineStr">
+        <is>
+          <t>2026-10-20 09:00</t>
+        </is>
+      </c>
+      <c r="B4019" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4019" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="4020">
+      <c r="A4020" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:00</t>
+        </is>
+      </c>
+      <c r="B4020" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4020" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="4021">
+      <c r="A4021" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00</t>
+        </is>
+      </c>
+      <c r="B4021" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4021" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="4022">
+      <c r="A4022" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:00</t>
+        </is>
+      </c>
+      <c r="B4022" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4022" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="4023">
+      <c r="A4023" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:00</t>
+        </is>
+      </c>
+      <c r="B4023" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4023" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="4024">
+      <c r="A4024" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:00</t>
+        </is>
+      </c>
+      <c r="B4024" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4024" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="4025">
+      <c r="A4025" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:00</t>
+        </is>
+      </c>
+      <c r="B4025" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4025" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="4026">
+      <c r="A4026" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:00</t>
+        </is>
+      </c>
+      <c r="B4026" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4026" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="4027">
+      <c r="A4027" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:00</t>
+        </is>
+      </c>
+      <c r="B4027" t="n">
+        <v>74</v>
+      </c>
+      <c r="C4027" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="4028">
+      <c r="A4028" t="inlineStr">
+        <is>
+          <t>2026-10-20 18:00</t>
+        </is>
+      </c>
+      <c r="B4028" t="n">
+        <v>72</v>
+      </c>
+      <c r="C4028" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4029">
+      <c r="A4029" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:00</t>
+        </is>
+      </c>
+      <c r="B4029" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4029" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="4030">
+      <c r="A4030" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:00</t>
+        </is>
+      </c>
+      <c r="B4030" t="n">
+        <v>71</v>
+      </c>
+      <c r="C4030" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4031">
+      <c r="A4031" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:00</t>
+        </is>
+      </c>
+      <c r="B4031" t="n">
+        <v>72</v>
+      </c>
+      <c r="C4031" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="4032">
+      <c r="A4032" t="inlineStr">
+        <is>
+          <t>2026-10-20 22:00</t>
+        </is>
+      </c>
+      <c r="B4032" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4032" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="4033">
+      <c r="A4033" t="inlineStr">
+        <is>
+          <t>2026-10-20 23:00</t>
+        </is>
+      </c>
+      <c r="B4033" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4033" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4033"/>
+  <dimension ref="A1:C4057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52861,6 +52861,318 @@
         <v>23.4</v>
       </c>
     </row>
+    <row r="4034">
+      <c r="A4034" t="inlineStr">
+        <is>
+          <t>2026-10-21 00:00</t>
+        </is>
+      </c>
+      <c r="B4034" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4034" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="4035">
+      <c r="A4035" t="inlineStr">
+        <is>
+          <t>2026-10-21 01:00</t>
+        </is>
+      </c>
+      <c r="B4035" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4035" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4036">
+      <c r="A4036" t="inlineStr">
+        <is>
+          <t>2026-10-21 02:00</t>
+        </is>
+      </c>
+      <c r="B4036" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4036" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="4037">
+      <c r="A4037" t="inlineStr">
+        <is>
+          <t>2026-10-21 03:00</t>
+        </is>
+      </c>
+      <c r="B4037" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4037" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="4038">
+      <c r="A4038" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:00</t>
+        </is>
+      </c>
+      <c r="B4038" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4038" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="4039">
+      <c r="A4039" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:00</t>
+        </is>
+      </c>
+      <c r="B4039" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4039" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="4040">
+      <c r="A4040" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:00</t>
+        </is>
+      </c>
+      <c r="B4040" t="n">
+        <v>72</v>
+      </c>
+      <c r="C4040" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4041">
+      <c r="A4041" t="inlineStr">
+        <is>
+          <t>2026-10-21 07:00</t>
+        </is>
+      </c>
+      <c r="B4041" t="n">
+        <v>72</v>
+      </c>
+      <c r="C4041" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="4042">
+      <c r="A4042" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:00</t>
+        </is>
+      </c>
+      <c r="B4042" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4042" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="4043">
+      <c r="A4043" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:00</t>
+        </is>
+      </c>
+      <c r="B4043" t="n">
+        <v>74</v>
+      </c>
+      <c r="C4043" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="4044">
+      <c r="A4044" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:00</t>
+        </is>
+      </c>
+      <c r="B4044" t="n">
+        <v>75</v>
+      </c>
+      <c r="C4044" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="4045">
+      <c r="A4045" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00</t>
+        </is>
+      </c>
+      <c r="B4045" t="n">
+        <v>75</v>
+      </c>
+      <c r="C4045" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="4046">
+      <c r="A4046" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="B4046" t="n">
+        <v>76</v>
+      </c>
+      <c r="C4046" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="4047">
+      <c r="A4047" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:00</t>
+        </is>
+      </c>
+      <c r="B4047" t="n">
+        <v>77</v>
+      </c>
+      <c r="C4047" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="4048">
+      <c r="A4048" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:00</t>
+        </is>
+      </c>
+      <c r="B4048" t="n">
+        <v>78</v>
+      </c>
+      <c r="C4048" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="4049">
+      <c r="A4049" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="B4049" t="n">
+        <v>79</v>
+      </c>
+      <c r="C4049" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4050">
+      <c r="A4050" t="inlineStr">
+        <is>
+          <t>2026-10-21 16:00</t>
+        </is>
+      </c>
+      <c r="B4050" t="n">
+        <v>82</v>
+      </c>
+      <c r="C4050" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="4051">
+      <c r="A4051" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:00</t>
+        </is>
+      </c>
+      <c r="B4051" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4051" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="4052">
+      <c r="A4052" t="inlineStr">
+        <is>
+          <t>2026-10-21 18:00</t>
+        </is>
+      </c>
+      <c r="B4052" t="n">
+        <v>125</v>
+      </c>
+      <c r="C4052" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="4053">
+      <c r="A4053" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:00</t>
+        </is>
+      </c>
+      <c r="B4053" t="n">
+        <v>126</v>
+      </c>
+      <c r="C4053" t="n">
+        <v>66.40000000000001</v>
+      </c>
+    </row>
+    <row r="4054">
+      <c r="A4054" t="inlineStr">
+        <is>
+          <t>2026-10-21 20:00</t>
+        </is>
+      </c>
+      <c r="B4054" t="n">
+        <v>106</v>
+      </c>
+      <c r="C4054" t="n">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="4055">
+      <c r="A4055" t="inlineStr">
+        <is>
+          <t>2026-10-21 21:00</t>
+        </is>
+      </c>
+      <c r="B4055" t="n">
+        <v>90</v>
+      </c>
+      <c r="C4055" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4056">
+      <c r="A4056" t="inlineStr">
+        <is>
+          <t>2026-10-21 22:00</t>
+        </is>
+      </c>
+      <c r="B4056" t="n">
+        <v>93</v>
+      </c>
+      <c r="C4056" t="n">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="4057">
+      <c r="A4057" t="inlineStr">
+        <is>
+          <t>2026-10-21 23:00</t>
+        </is>
+      </c>
+      <c r="B4057" t="n">
+        <v>95</v>
+      </c>
+      <c r="C4057" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4057"/>
+  <dimension ref="A1:C4081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53173,6 +53173,318 @@
         <v>32.6</v>
       </c>
     </row>
+    <row r="4058">
+      <c r="A4058" t="inlineStr">
+        <is>
+          <t>2026-10-22 00:00</t>
+        </is>
+      </c>
+      <c r="B4058" t="n">
+        <v>95</v>
+      </c>
+      <c r="C4058" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4059">
+      <c r="A4059" t="inlineStr">
+        <is>
+          <t>2026-10-22 01:00</t>
+        </is>
+      </c>
+      <c r="B4059" t="n">
+        <v>96</v>
+      </c>
+      <c r="C4059" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4060">
+      <c r="A4060" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:00</t>
+        </is>
+      </c>
+      <c r="B4060" t="n">
+        <v>97</v>
+      </c>
+      <c r="C4060" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="4061">
+      <c r="A4061" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:00</t>
+        </is>
+      </c>
+      <c r="B4061" t="n">
+        <v>98</v>
+      </c>
+      <c r="C4061" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="4062">
+      <c r="A4062" t="inlineStr">
+        <is>
+          <t>2026-10-22 04:00</t>
+        </is>
+      </c>
+      <c r="B4062" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4062" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="4063">
+      <c r="A4063" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:00</t>
+        </is>
+      </c>
+      <c r="B4063" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4063" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="4064">
+      <c r="A4064" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:00</t>
+        </is>
+      </c>
+      <c r="B4064" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4064" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="4065">
+      <c r="A4065" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:00</t>
+        </is>
+      </c>
+      <c r="B4065" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4065" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="4066">
+      <c r="A4066" t="inlineStr">
+        <is>
+          <t>2026-10-22 08:00</t>
+        </is>
+      </c>
+      <c r="B4066" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4066" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="4067">
+      <c r="A4067" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:00</t>
+        </is>
+      </c>
+      <c r="B4067" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4067" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="4068">
+      <c r="A4068" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="B4068" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4068" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="4069">
+      <c r="A4069" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:00</t>
+        </is>
+      </c>
+      <c r="B4069" t="n">
+        <v>102</v>
+      </c>
+      <c r="C4069" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="4070">
+      <c r="A4070" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="B4070" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4070" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="4071">
+      <c r="A4071" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:00</t>
+        </is>
+      </c>
+      <c r="B4071" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4071" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="4072">
+      <c r="A4072" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:00</t>
+        </is>
+      </c>
+      <c r="B4072" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4072" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="4073">
+      <c r="A4073" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="B4073" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4073" t="n">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="4074">
+      <c r="A4074" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:00</t>
+        </is>
+      </c>
+      <c r="B4074" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4074" t="n">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="4075">
+      <c r="A4075" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:00</t>
+        </is>
+      </c>
+      <c r="B4075" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4075" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="4076">
+      <c r="A4076" t="inlineStr">
+        <is>
+          <t>2026-10-22 18:00</t>
+        </is>
+      </c>
+      <c r="B4076" t="n">
+        <v>106</v>
+      </c>
+      <c r="C4076" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="4077">
+      <c r="A4077" t="inlineStr">
+        <is>
+          <t>2026-10-22 19:00</t>
+        </is>
+      </c>
+      <c r="B4077" t="n">
+        <v>107</v>
+      </c>
+      <c r="C4077" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="4078">
+      <c r="A4078" t="inlineStr">
+        <is>
+          <t>2026-10-22 20:00</t>
+        </is>
+      </c>
+      <c r="B4078" t="n">
+        <v>107</v>
+      </c>
+      <c r="C4078" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="4079">
+      <c r="A4079" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:00</t>
+        </is>
+      </c>
+      <c r="B4079" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4079" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="4080">
+      <c r="A4080" t="inlineStr">
+        <is>
+          <t>2026-10-22 22:00</t>
+        </is>
+      </c>
+      <c r="B4080" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4080" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="4081">
+      <c r="A4081" t="inlineStr">
+        <is>
+          <t>2026-10-22 23:00</t>
+        </is>
+      </c>
+      <c r="B4081" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4081" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hcm_air_quality_log.xlsx
+++ b/hcm_air_quality_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4081"/>
+  <dimension ref="A1:C4105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53485,6 +53485,318 @@
         <v>50.2</v>
       </c>
     </row>
+    <row r="4082">
+      <c r="A4082" t="inlineStr">
+        <is>
+          <t>2026-10-23 00:00</t>
+        </is>
+      </c>
+      <c r="B4082" t="n">
+        <v>107</v>
+      </c>
+      <c r="C4082" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="4083">
+      <c r="A4083" t="inlineStr">
+        <is>
+          <t>2026-10-23 01:00</t>
+        </is>
+      </c>
+      <c r="B4083" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4083" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4084">
+      <c r="A4084" t="inlineStr">
+        <is>
+          <t>2026-10-23 02:00</t>
+        </is>
+      </c>
+      <c r="B4084" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4084" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="4085">
+      <c r="A4085" t="inlineStr">
+        <is>
+          <t>2026-10-23 03:00</t>
+        </is>
+      </c>
+      <c r="B4085" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4085" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4086">
+      <c r="A4086" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:00</t>
+        </is>
+      </c>
+      <c r="B4086" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4086" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="4087">
+      <c r="A4087" t="inlineStr">
+        <is>
+          <t>2026-10-23 05:00</t>
+        </is>
+      </c>
+      <c r="B4087" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4087" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="4088">
+      <c r="A4088" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:00</t>
+        </is>
+      </c>
+      <c r="B4088" t="n">
+        <v>109</v>
+      </c>
+      <c r="C4088" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="4089">
+      <c r="A4089" t="inlineStr">
+        <is>
+          <t>2026-10-23 07:00</t>
+        </is>
+      </c>
+      <c r="B4089" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4089" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4090">
+      <c r="A4090" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:00</t>
+        </is>
+      </c>
+      <c r="B4090" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4090" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="4091">
+      <c r="A4091" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:00</t>
+        </is>
+      </c>
+      <c r="B4091" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4091" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="4092">
+      <c r="A4092" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:00</t>
+        </is>
+      </c>
+      <c r="B4092" t="n">
+        <v>109</v>
+      </c>
+      <c r="C4092" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="4093">
+      <c r="A4093" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:00</t>
+        </is>
+      </c>
+      <c r="B4093" t="n">
+        <v>109</v>
+      </c>
+      <c r="C4093" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="4094">
+      <c r="A4094" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:00</t>
+        </is>
+      </c>
+      <c r="B4094" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4094" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="4095">
+      <c r="A4095" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:00</t>
+        </is>
+      </c>
+      <c r="B4095" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4095" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="4096">
+      <c r="A4096" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:00</t>
+        </is>
+      </c>
+      <c r="B4096" t="n">
+        <v>107</v>
+      </c>
+      <c r="C4096" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="4097">
+      <c r="A4097" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:00</t>
+        </is>
+      </c>
+      <c r="B4097" t="n">
+        <v>106</v>
+      </c>
+      <c r="C4097" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="4098">
+      <c r="A4098" t="inlineStr">
+        <is>
+          <t>2026-10-23 16:00</t>
+        </is>
+      </c>
+      <c r="B4098" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4098" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="4099">
+      <c r="A4099" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:00</t>
+        </is>
+      </c>
+      <c r="B4099" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4099" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="4100">
+      <c r="A4100" t="inlineStr">
+        <is>
+          <t>2026-10-23 18:00</t>
+        </is>
+      </c>
+      <c r="B4100" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4100" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4101">
+      <c r="A4101" t="inlineStr">
+        <is>
+          <t>2026-10-23 19:00</t>
+        </is>
+      </c>
+      <c r="B4101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4101" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4102">
+      <c r="A4102" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:00</t>
+        </is>
+      </c>
+      <c r="B4102" t="n">
+        <v>97</v>
+      </c>
+      <c r="C4102" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="4103">
+      <c r="A4103" t="inlineStr">
+        <is>
+          <t>2026-10-23 21:00</t>
+        </is>
+      </c>
+      <c r="B4103" t="n">
+        <v>95</v>
+      </c>
+      <c r="C4103" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="4104">
+      <c r="A4104" t="inlineStr">
+        <is>
+          <t>2026-10-23 22:00</t>
+        </is>
+      </c>
+      <c r="B4104" t="n">
+        <v>93</v>
+      </c>
+      <c r="C4104" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="4105">
+      <c r="A4105" t="inlineStr">
+        <is>
+          <t>2026-10-23 23:00</t>
+        </is>
+      </c>
+      <c r="B4105" t="n">
+        <v>91</v>
+      </c>
+      <c r="C4105" t="n">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
